--- a/evaluation_results/Evaluation_Final_Results.xlsx
+++ b/evaluation_results/Evaluation_Final_Results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,11 @@
           <t>latency</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -501,73 +506,42 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho được hiểu là gì trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 03.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho là những tài sản được giữ để bán trong kỳ sản xuất, kinh doanh bình thường; đang trong quá trình sản xuất, kinh doanh dở dang; hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ để sử dụng trong quá trình sản xuất, kinh doanh hoặc cung cấp dịch vụ. Hàng tồn kho bao gồm hàng hóa mua về để bán, thành phẩm tồn kho và gửi đi bán, sản phẩm dở dang, nguyên liệu/vật liệu/công cụ/dụng cụ tồn kho hoặc gửi đi gia công, hàng mua đang đi đường và chi phí dịch vụ dở dang. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 03.)</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>local</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho theo Chuẩn mực kế toán Việt Nam (VAS) là gì?</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>VAS, hàng tồn kho</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 16.
-2. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ TRÌNH BÀY BÁO CÁO TÀI CHÍNH ➔ 28.
-3. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ XÁC ĐỊNH GIÁ TRỊ HÀNG TỒN KHO ➔ 04.
-4. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ TRỊ THUẦN CÓ THỂ THỰC HIỆN ĐƯỢC VÀ LẬP DỰ PHÒNG GIẢM GIÁ HÀNG TỒN KHO ➔ 23.
-5. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 02.
-6. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 03.
-7. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 17.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>--- NGUỒN 1 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; NỘI DUNG CHUẨN MỰC &gt; PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO &gt; 16.】
-NỘI DUNG: Phương pháp nhập trước, xuất trước áp dụng dựa trên giả định là hàng tồn kho được mua trước hoặc sản xuất trước thì được xuất trước, và hàng tồn kho còn lại cuối kỳ là hàng tồn kho được mua hoặc sản xuất gần thời điểm cuối kỳ. Theo phương pháp này thì giá trị hàng xuất kho được tính theo giá của lô hàng nhập kho ở thời điểm đầu kỳ hoặc gần đầu kỳ, giá trị của hàng tồn kho được tính theo giá của hàng nhập kho ở thời điểm cuối kỳ hoặc gần cuối kỳ còn tồn kho.
---- NGUỒN 2 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; NỘI DUNG CHUẨN MỰC &gt; TRÌNH BÀY BÁO CÁO TÀI CHÍNH &gt; 28.】
-NỘI DUNG: Trường hợp doanh nghiệp tính giá trị hàng tồn kho theo phương pháp nhập sau, xuất trước thì báo cáo tài chính phải phản ánh số chênh lệch giữa giá trị hàng tồn kho trình bày trong bảng cân đối kế toán với: (a) Giá trị hàng tồn kho cuối kỳ được tính theo phương pháp nhập trước, xuất trước (nếu giá trị hàng tồn kho cuối kỳ tính theo phương pháp nhập trước, xuất trước nhỏ hơn giá trị hàng tồn kho cuối kỳ tính theo phương pháp bình quân gia quyền và giá trị thuần có thể thực hiện được); hoặc Với giá trị hàng tồn kho cuối kỳ được tính theo phương pháp bình quân gia quyền (nếu giá trị hàng tồn kho cuối kỳ tính theo phương pháp bình quân gia quyền nhỏ hơn giá trị hàng tồn kho cuối kỳ tính theo phương pháp nhập trước, xuất trước và giá trị thuần có thể thực hiện được); hoặc Với giá trị hàng tồn kho cuối kỳ được tính theo giá trị thuần có thể thực hiện được (nếu giá trị hàng tồn kho cuối kỳ tính theo giá trị thuần có thể thực hiện được nhỏ hơn giá trị hàng tồn kho tính theo phương pháp nhập trước, xuất trước và phương pháp bình quân gia quyền); hoặc (b) Giá trị hiện hành của hàng tồn kho cuối kỳ tại ngày lập bảng cân đối kế toán (nếu giá trị hiện hành của hàng tồn kho tại ngày lập bảng cân đối kế toán nhỏ hơn giá trị thuần có thể thực hiện được); hoặc với giá trị thuần có thể thực hiện được (nếu giá trị hàng tồn kho cuối kỳ tính theo giá trị thuần có thể thực hiện được nhỏ hơn giá trị hàng tồn kho cuối kỳ tính theo giá trị hiện hành tại ngày lập bảng cân đối kế toán).
---- NGUỒN 3 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; NỘI DUNG CHUẨN MỰC &gt; XÁC ĐỊNH GIÁ TRỊ HÀNG TỒN KHO &gt; 04.】
-NỘI DUNG: Hàng tồn kho được tính theo giá gốc. Trường hợp giá trị thuần có thể thực hiện được thấp hơn giá gốc thì phải tính theo giá trị thuần có thể thực hiện được.
---- NGUỒN 4 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; NỘI DUNG CHUẨN MỰC &gt; GIÁ TRỊ THUẦN CÓ THỂ THỰC HIỆN ĐƯỢC VÀ LẬP DỰ PHÒNG GIẢM GIÁ HÀNG TỒN KHO &gt; 23.】
-NỘI DUNG: Cuối kỳ kế toán năm tiếp theo phải thực hiện đánh giá mới về giá trị thuần có thể thực hiện được của hàng tồn kho cuối năm đó. Trường hợp cuối kỳ kế toán năm nay, nếu khoản dự phòng giảm giá hàng tồn kho phải lập thấp hơn khoản dự phòng giảm giá hàng tồn kho đã lập ở cuối kỳ kế toán năm trước thì số chênh lệch lớn hơn phải được hoàn nhập (Theo quy định ở đoạn 24) để đảm bảo cho giá trị của hàng tồn kho phản ánh trên báo cáo tài chính là theo giá gốc (nếu giá gốc nhỏ hơn giá trị thuần có thể thực hiện được) hoặc theo giá trị thuần có thể thực hiện được (nếu giá gốc lớn hơn giá trị thuần có thể thực hiện được).
---- NGUỒN 5 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; QUY ĐỊNH CHUNG &gt; 02.】
-NỘI DUNG: Chuẩn mực này áp dụng cho kế toán hàng tồn kho theo nguyên tắc giá gốc trừ khi có chuẩn mực kế toán khác quy định cho phép áp dụng phương pháp kế toán khác cho hàng tồn kho.
---- NGUỒN 6 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; QUY ĐỊNH CHUNG &gt; 03.】
-NỘI DUNG: Các thuật ngữ trong chuẩn mực này được hiểu như sau: Hàng tồn kho: Là những tài sản: (a) Được giữ để bán trong kỳ sản xuất, kinh doanh bình thường; (b) Đang trong quá trình sản xuất, kinh doanh dở dang; (c) Nguyên liệu, vật liệu, công cụ, dụng cụ để sử dụng trong quá trình sản xuất, kinh doanh hoặc cung cấp dịch vụ. Hàng tồn kho bao gồm: - Hàng hóa mua về để bán: Hàng hóa tồn kho, hàng mua đang đi trên đường, hàng gửi đi bán, hàng hóa gửi đi gia công chế biến; - Thành phẩm tồn kho và thành phẩm gửi đi bán; - Sản phẩm dở dang: Sản phẩm chưa hoàn thành và sản phẩm hoàn thành chưa làm thủ tục nhập kho thành phẩm; - Nguyên liệu, vật liệu, công cụ, dụng cụ tồn kho, gửi đi gia công chế biến và đã mua đang đi trên đường; - Chi phí dịch vụ dở dang. Giá trị thuần có thể thực hiện được: Là giá bán ước tính của hàng tồn kho trong kỳ sản xuất, kinh doanh bình thường trừ (-) chi phí ước tính để hoàn thành sản phẩm và chi phí ước tính cần thiết cho việc tiêu thụ chúng. Giá hiện hành: Là khoản tiền phải trả để mua một loại hàng tồn kho tương tự tại ngày lập bảng cân đối kế toán.
---- NGUỒN 7 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; NỘI DUNG CHUẨN MỰC &gt; PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO &gt; 17.】
-NỘI DUNG: Phương pháp nhập sau, xuất trước áp dụng dựa trên giả định là hàng tồn kho được mua sau hoặc sản xuất sau thì được xuất trước, và hàng tồn kho còn lại cuối kỳ là hàng tồn kho được mua hoặc sản xuất trước đó. Theo phương pháp này thì giá trị hàng xuất kho được tính theo giá của lô hàng nhập sau hoặc gần sau cùng, giá trị của hàng tồn kho được tính theo giá của hàng nhập kho đầu kỳ hoặc gần đầu kỳ còn tồn kho.</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Hàng tồn kho được định nghĩa là những tài sản mà doanh nghiệp giữ trữ với mục đích bán trong kỳ sản xuất, kinh doanh bình thường. Dựa trên các thông tin từ các nguồn tri thức cung cấp, hàng tồn kho bao gồm:
-- Hàng hóa mua về để bán: như hàng hóa tồn kho, hàng mua đang đi trên đường, hàng gửi đi bán, hàng hóa gửi đi gia công chế biến.
-- Thành phẩm tồn kho và thành phẩm gửi đi bán.
-- Sản phẩm dở dang: sản phẩm chưa hoàn thành và sản phẩm hoàn thành chưa làm thủ tục nhập kho thành phẩm.
-- Nguyên liệu, vật liệu, công cụ, dụng cụ tồn kho, gửi đi gia công chế biến và đã mua đang đi trên đường.
-- Chi phí dịch vụ dở dang.
-Điều này được xác định theo chuẩn mực số 02 - Hàng tồn kho (VAS 02), trong đó các thuật ngữ như "hàng tồn kho" được hiểu là những tài sản mà doanh nghiệp giữ trữ với mục đích bán trong kỳ sản xuất, kinh doanh bình thường.</t>
+          <t>LỖI: '\n    "standalone_query"'</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>25.57</v>
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -583,66 +557,42 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho được hiểu là gì trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 03.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho là những tài sản được giữ để bán trong kỳ sản xuất, kinh doanh bình thường; đang trong quá trình sản xuất, kinh doanh dở dang; hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ để sử dụng trong quá trình sản xuất, kinh doanh hoặc cung cấp dịch vụ. Hàng tồn kho bao gồm hàng hóa mua về để bán, thành phẩm tồn kho và gửi đi bán, sản phẩm dở dang, nguyên liệu/vật liệu/công cụ/dụng cụ tồn kho hoặc gửi đi gia công, hàng mua đang đi đường và chi phí dịch vụ dở dang. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 03.)</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>hybrid</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho theo Chuẩn mực kế toán Việt Nam (VAS) là gì?</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>VAS, hàng tồn kho</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ TRÌNH BÀY BÁO CÁO TÀI CHÍNH ➔ 28.
-2. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ XÁC ĐỊNH GIÁ TRỊ HÀNG TỒN KHO ➔ 04.
-3. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ TRỊ THUẦN CÓ THỂ THỰC HIỆN ĐƯỢC VÀ LẬP DỰ PHÒNG GIẢM GIÁ HÀNG TỒN KHO ➔ 23.
-4. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 16.
-5. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 17.
-6. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 02.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>--- NGUỒN 1 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; NỘI DUNG CHUẨN MỰC &gt; TRÌNH BÀY BÁO CÁO TÀI CHÍNH &gt; 28.】
-NỘI DUNG: Trường hợp doanh nghiệp tính giá trị hàng tồn kho theo phương pháp nhập sau, xuất trước thì báo cáo tài chính phải phản ánh số chênh lệch giữa giá trị hàng tồn kho trình bày trong bảng cân đối kế toán với: (a) Giá trị hàng tồn kho cuối kỳ được tính theo phương pháp nhập trước, xuất trước (nếu giá trị hàng tồn kho cuối kỳ tính theo phương pháp nhập trước, xuất trước nhỏ hơn giá trị hàng tồn kho cuối kỳ tính theo phương pháp bình quân gia quyền và giá trị thuần có thể thực hiện được); hoặc Với giá trị hàng tồn kho cuối kỳ được tính theo phương pháp bình quân gia quyền (nếu giá trị hàng tồn kho cuối kỳ tính theo phương pháp bình quân gia quyền nhỏ hơn giá trị hàng tồn kho cuối kỳ tính theo phương pháp nhập trước, xuất trước và giá trị thuần có thể thực hiện được); hoặc Với giá trị hàng tồn kho cuối kỳ được tính theo giá trị thuần có thể thực hiện được (nếu giá trị hàng tồn kho cuối kỳ tính theo giá trị thuần có thể thực hiện được nhỏ hơn giá trị hàng tồn kho tính theo phương pháp nhập trước, xuất trước và phương pháp bình quân gia quyền); hoặc (b) Giá trị hiện hành của hàng tồn kho cuối kỳ tại ngày lập bảng cân đối kế toán (nếu giá trị hiện hành của hàng tồn kho tại ngày lập bảng cân đối kế toán nhỏ hơn giá trị thuần có thể thực hiện được); hoặc với giá trị thuần có thể thực hiện được (nếu giá trị hàng tồn kho cuối kỳ tính theo giá trị thuần có thể thực hiện được nhỏ hơn giá trị hàng tồn kho cuối kỳ tính theo giá trị hiện hành tại ngày lập bảng cân đối kế toán).
---- NGUỒN 2 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; NỘI DUNG CHUẨN MỰC &gt; XÁC ĐỊNH GIÁ TRỊ HÀNG TỒN KHO &gt; 04.】
-NỘI DUNG: Hàng tồn kho được tính theo giá gốc. Trường hợp giá trị thuần có thể thực hiện được thấp hơn giá gốc thì phải tính theo giá trị thuần có thể thực hiện được.
---- NGUỒN 3 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; NỘI DUNG CHUẨN MỰC &gt; GIÁ TRỊ THUẦN CÓ THỂ THỰC HIỆN ĐƯỢC VÀ LẬP DỰ PHÒNG GIẢM GIÁ HÀNG TỒN KHO &gt; 23.】
-NỘI DUNG: Cuối kỳ kế toán năm tiếp theo phải thực hiện đánh giá mới về giá trị thuần có thể thực hiện được của hàng tồn kho cuối năm đó. Trường hợp cuối kỳ kế toán năm nay, nếu khoản dự phòng giảm giá hàng tồn kho phải lập thấp hơn khoản dự phòng giảm giá hàng tồn kho đã lập ở cuối kỳ kế toán năm trước thì số chênh lệch lớn hơn phải được hoàn nhập (Theo quy định ở đoạn 24) để đảm bảo cho giá trị của hàng tồn kho phản ánh trên báo cáo tài chính là theo giá gốc (nếu giá gốc nhỏ hơn giá trị thuần có thể thực hiện được) hoặc theo giá trị thuần có thể thực hiện được (nếu giá gốc lớn hơn giá trị thuần có thể thực hiện được).
---- NGUỒN 4 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; NỘI DUNG CHUẨN MỰC &gt; PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO &gt; 16.】
-NỘI DUNG: Phương pháp nhập trước, xuất trước áp dụng dựa trên giả định là hàng tồn kho được mua trước hoặc sản xuất trước thì được xuất trước, và hàng tồn kho còn lại cuối kỳ là hàng tồn kho được mua hoặc sản xuất gần thời điểm cuối kỳ. Theo phương pháp này thì giá trị hàng xuất kho được tính theo giá của lô hàng nhập kho ở thời điểm đầu kỳ hoặc gần đầu kỳ, giá trị của hàng tồn kho được tính theo giá của hàng nhập kho ở thời điểm cuối kỳ hoặc gần cuối kỳ còn tồn kho.
---- NGUỒN 5 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; NỘI DUNG CHUẨN MỰC &gt; PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO &gt; 17.】
-NỘI DUNG: Phương pháp nhập sau, xuất trước áp dụng dựa trên giả định là hàng tồn kho được mua sau hoặc sản xuất sau thì được xuất trước, và hàng tồn kho còn lại cuối kỳ là hàng tồn kho được mua hoặc sản xuất trước đó. Theo phương pháp này thì giá trị hàng xuất kho được tính theo giá của lô hàng nhập sau hoặc gần sau cùng, giá trị của hàng tồn kho được tính theo giá của hàng nhập kho đầu kỳ hoặc gần đầu kỳ còn tồn kho.
---- NGUỒN 6 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; QUY ĐỊNH CHUNG &gt; 02.】
-NỘI DUNG: Chuẩn mực này áp dụng cho kế toán hàng tồn kho theo nguyên tắc giá gốc trừ khi có chuẩn mực kế toán khác quy định cho phép áp dụng phương pháp kế toán khác cho hàng tồn kho.</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Hàng tồn kho trong ngữ cảnh này được hiểu là các sản phẩm hoặc nguyên vật liệu mà doanh nghiệp đang giữ trữ, chờ bán ra thị trường. Hàng tồn kho có thể bao gồm cả hàng hóa đã mua từ bên ngoài và hàng hóa do công ty sản xuất trong quá trình hoạt động kinh doanh.
-Để xác định giá trị của hàng tồn kho, doanh nghiệp thường áp dụng một số phương pháp tính giá trị khác nhau như: nhập trước, xuất trước; nhập sau, xuất trước. Phương pháp này được sử dụng dựa trên giả định rằng hàng hóa được mua hoặc sản xuất trước sẽ được bán ra trước và hàng còn lại cuối kỳ là hàng đã mua hoặc sản xuất gần thời điểm cuối kỳ.
-Trong báo cáo tài chính, giá trị của hàng tồn kho thường được trình bày theo phương pháp nhập trước, xuất trước. Tuy nhiên, doanh nghiệp có thể tính giá trị hàng tồn kho theo các phương pháp khác như: nhập sau, xuất trước; hoặc dựa trên giá gốc (giá trị thuần có thể thực hiện được) nếu giá trị này thấp hơn giá gốc.
-Để đảm bảo thông tin về giá trị của hàng tồn kho phản ánh chính xác trong báo cáo tài chính, doanh nghiệp cần phải đánh giá lại giá trị thuần có thể thực hiện được của hàng tồn kho cuối kỳ mỗi năm. Nếu dự phòng giảm giá hàng tồn kho đã lập thấp hơn so với dự phòng giảm giá hàng tồn kho từ năm trước, số chênh lệch lớn hơn sẽ được hoàn nhập để đảm bảo giá trị của hàng tồn kho phản ánh trên báo cáo tài chính là theo giá gốc (nếu giá gốc nhỏ hơn giá trị thuần có thể thực hiện được) hoặc theo giá trị thuần có thể thực hiện được (nếu giá gốc lớn hơn giá trị thuần có thể thực hiện được).</t>
+          <t>LỖI: '\n    "standalone_query"'</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>38.41</v>
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -658,77 +608,5517 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho được hiểu là gì trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 03.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho là những tài sản được giữ để bán trong kỳ sản xuất, kinh doanh bình thường; đang trong quá trình sản xuất, kinh doanh dở dang; hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ để sử dụng trong quá trình sản xuất, kinh doanh hoặc cung cấp dịch vụ. Hàng tồn kho bao gồm hàng hóa mua về để bán, thành phẩm tồn kho và gửi đi bán, sản phẩm dở dang, nguyên liệu/vật liệu/công cụ/dụng cụ tồn kho hoặc gửi đi gia công, hàng mua đang đi đường và chi phí dịch vụ dở dang. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 03.)</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>cloud</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho được định nghĩa như thế nào theo Chuẩn mực kế toán Việt Nam (VAS)?</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho, định nghĩa, VAS</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>1. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ XÁC ĐỊNH GIÁ TRỊ HÀNG TỒN KHO ➔ 04.
-2. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 16.
-3. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ TRỊ THUẦN CÓ THỂ THỰC HIỆN ĐƯỢC VÀ LẬP DỰ PHÒNG GIẢM GIÁ HÀNG TỒN KHO ➔ 23.
-4. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ TRÌNH BÀY BÁO CÁO TÀI CHÍNH ➔ 28.
-5. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 02.
-6. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 03.
-7. CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ NỘI DUNG CHUẨN MỰC ➔ Chuyển đổi mục đích sử dụng ➔ 23.
-8. CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 01.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>--- NGUỒN 1 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; NỘI DUNG CHUẨN MỰC &gt; XÁC ĐỊNH GIÁ TRỊ HÀNG TỒN KHO &gt; 04.】
-NỘI DUNG: Hàng tồn kho được tính theo giá gốc. Trường hợp giá trị thuần có thể thực hiện được thấp hơn giá gốc thì phải tính theo giá trị thuần có thể thực hiện được.
---- NGUỒN 2 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; NỘI DUNG CHUẨN MỰC &gt; PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO &gt; 16.】
-NỘI DUNG: Phương pháp nhập trước, xuất trước áp dụng dựa trên giả định là hàng tồn kho được mua trước hoặc sản xuất trước thì được xuất trước, và hàng tồn kho còn lại cuối kỳ là hàng tồn kho được mua hoặc sản xuất gần thời điểm cuối kỳ. Theo phương pháp này thì giá trị hàng xuất kho được tính theo giá của lô hàng nhập kho ở thời điểm đầu kỳ hoặc gần đầu kỳ, giá trị của hàng tồn kho được tính theo giá của hàng nhập kho ở thời điểm cuối kỳ hoặc gần cuối kỳ còn tồn kho.
---- NGUỒN 3 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; NỘI DUNG CHUẨN MỰC &gt; GIÁ TRỊ THUẦN CÓ THỂ THỰC HIỆN ĐƯỢC VÀ LẬP DỰ PHÒNG GIẢM GIÁ HÀNG TỒN KHO &gt; 23.】
-NỘI DUNG: Cuối kỳ kế toán năm tiếp theo phải thực hiện đánh giá mới về giá trị thuần có thể thực hiện được của hàng tồn kho cuối năm đó. Trường hợp cuối kỳ kế toán năm nay, nếu khoản dự phòng giảm giá hàng tồn kho phải lập thấp hơn khoản dự phòng giảm giá hàng tồn kho đã lập ở cuối kỳ kế toán năm trước thì số chênh lệch lớn hơn phải được hoàn nhập (Theo quy định ở đoạn 24) để đảm bảo cho giá trị của hàng tồn kho phản ánh trên báo cáo tài chính là theo giá gốc (nếu giá gốc nhỏ hơn giá trị thuần có thể thực hiện được) hoặc theo giá trị thuần có thể thực hiện được (nếu giá gốc lớn hơn giá trị thuần có thể thực hiện được).
---- NGUỒN 4 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; NỘI DUNG CHUẨN MỰC &gt; TRÌNH BÀY BÁO CÁO TÀI CHÍNH &gt; 28.】
-NỘI DUNG: Trường hợp doanh nghiệp tính giá trị hàng tồn kho theo phương pháp nhập sau, xuất trước thì báo cáo tài chính phải phản ánh số chênh lệch giữa giá trị hàng tồn kho trình bày trong bảng cân đối kế toán với: (a) Giá trị hàng tồn kho cuối kỳ được tính theo phương pháp nhập trước, xuất trước (nếu giá trị hàng tồn kho cuối kỳ tính theo phương pháp nhập trước, xuất trước nhỏ hơn giá trị hàng tồn kho cuối kỳ tính theo phương pháp bình quân gia quyền và giá trị thuần có thể thực hiện được); hoặc Với giá trị hàng tồn kho cuối kỳ được tính theo phương pháp bình quân gia quyền (nếu giá trị hàng tồn kho cuối kỳ tính theo phương pháp bình quân gia quyền nhỏ hơn giá trị hàng tồn kho cuối kỳ tính theo phương pháp nhập trước, xuất trước và giá trị thuần có thể thực hiện được); hoặc Với giá trị hàng tồn kho cuối kỳ được tính theo giá trị thuần có thể thực hiện được (nếu giá trị hàng tồn kho cuối kỳ tính theo giá trị thuần có thể thực hiện được nhỏ hơn giá trị hàng tồn kho tính theo phương pháp nhập trước, xuất trước và phương pháp bình quân gia quyền); hoặc (b) Giá trị hiện hành của hàng tồn kho cuối kỳ tại ngày lập bảng cân đối kế toán (nếu giá trị hiện hành của hàng tồn kho tại ngày lập bảng cân đối kế toán nhỏ hơn giá trị thuần có thể thực hiện được); hoặc với giá trị thuần có thể thực hiện được (nếu giá trị hàng tồn kho cuối kỳ tính theo giá trị thuần có thể thực hiện được nhỏ hơn giá trị hàng tồn kho cuối kỳ tính theo giá trị hiện hành tại ngày lập bảng cân đối kế toán).
---- NGUỒN 5 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; QUY ĐỊNH CHUNG &gt; 02.】
-NỘI DUNG: Chuẩn mực này áp dụng cho kế toán hàng tồn kho theo nguyên tắc giá gốc trừ khi có chuẩn mực kế toán khác quy định cho phép áp dụng phương pháp kế toán khác cho hàng tồn kho.
---- NGUỒN 6 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; QUY ĐỊNH CHUNG &gt; 03.】
-NỘI DUNG: Các thuật ngữ trong chuẩn mực này được hiểu như sau: Hàng tồn kho: Là những tài sản: (a) Được giữ để bán trong kỳ sản xuất, kinh doanh bình thường; (b) Đang trong quá trình sản xuất, kinh doanh dở dang; (c) Nguyên liệu, vật liệu, công cụ, dụng cụ để sử dụng trong quá trình sản xuất, kinh doanh hoặc cung cấp dịch vụ. Hàng tồn kho bao gồm: - Hàng hóa mua về để bán: Hàng hóa tồn kho, hàng mua đang đi trên đường, hàng gửi đi bán, hàng hóa gửi đi gia công chế biến; - Thành phẩm tồn kho và thành phẩm gửi đi bán; - Sản phẩm dở dang: Sản phẩm chưa hoàn thành và sản phẩm hoàn thành chưa làm thủ tục nhập kho thành phẩm; - Nguyên liệu, vật liệu, công cụ, dụng cụ tồn kho, gửi đi gia công chế biến và đã mua đang đi trên đường; - Chi phí dịch vụ dở dang. Giá trị thuần có thể thực hiện được: Là giá bán ước tính của hàng tồn kho trong kỳ sản xuất, kinh doanh bình thường trừ (-) chi phí ước tính để hoàn thành sản phẩm và chi phí ước tính cần thiết cho việc tiêu thụ chúng. Giá hiện hành: Là khoản tiền phải trả để mua một loại hàng tồn kho tương tự tại ngày lập bảng cân đối kế toán.
---- NGUỒN 7 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ &gt; NỘI DUNG CHUẨN MỰC &gt; Chuyển đổi mục đích sử dụng &gt; 23.】
-NỘI DUNG: Việc chuyển từ bất động sản chủ sở hữu sử dụng thành bất động sản đầu tư hoặc từ bất động sản đầu tư sang bất động sản chủ sở hữu sử dụng hay hàng tồn kho chỉ khi có sự thay đổi về mục đích sử dụng như các trường hợp sau: a. Bất động sản đầu tư chuyển thành bất động sản chủ sở hữu sử dụng khi chủ sở hữu bắt đầu sử dụng tài sản này; b. Bất động sản đầu tư chuyển thành hàng tồn kho khi chủ sở hữu bắt đầu triển khai cho mục đích bán; c. Bất động sản chủ sở hữu sử dụng chuyển thành bất động sản đầu tư khi chủ sở hữu kết thúc sử dụng tài sản đó; d. Hàng tồn kho chuyển thành bất động sản đầu tư khi chủ sở hữu bắt đầu cho bên khác thuê hoạt động; e. Bất động sản xây dựng chuyển thành bất động sản đầu tư khi kết thúc giai đoạn xây dựng, bàn giao đưa vào đầu tư (Trong giai đoạn xây dựng phải kế toán theo Chuẩn mực kế toán số 03 “ Tài sản cố định hữu hình”).
---- NGUỒN 8 ---
-【NGỮ CẢNH: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; QUY ĐỊNH CHUNG &gt; 01.】
-NỘI DUNG: Mục đích của chuẩn mực này là quy định và hướng dẫn các nguyên tắc và phương pháp kế toán hàng tồn kho, gồm: Xác định giá trị và kế toán hàng tồn kho vào chi phí; Ghi giảm giá trị hàng tồn kho cho phù hợp với giá trị thuần có thể thực hiện được và phương pháp tính giá trị hàng tồn kho làm cơ sở ghi sổ kế toán và lập báo cáo tài chính.</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Hàng tồn kho là những tài sản được giữ để bán trong kỳ sản xuất, kinh doanh bình thường; đang trong quá trình sản xuất, kinh doanh dở dang; hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ để sử dụng trong quá trình sản xuất, kinh doanh hoặc cung cấp dịch vụ. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; QUY ĐỊNH CHUNG &gt; 03.)
-Hàng tồn kho bao gồm:
-*   Hàng hóa mua về để bán, bao gồm hàng hóa tồn kho, hàng mua đang đi trên đường, hàng gửi đi bán, hàng hóa gửi đi gia công chế biến.
-*   Thành phẩm tồn kho và thành phẩm gửi đi bán.
-*   Sản phẩm dở dang, bao gồm sản phẩm chưa hoàn thành và sản phẩm hoàn thành chưa làm thủ tục nhập kho thành phẩm.
-*   Nguyên liệu, vật liệu, công cụ, dụng cụ tồn kho, gửi đi gia công chế biến và đã mua đang đi trên đường.
-*   Chi phí dịch vụ dở dang. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO &gt; QUY ĐỊNH CHUNG &gt; 03.)</t>
+          <t>LỖI: '\n    "standalone_query"'</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>14.5</v>
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Giá gốc hàng tồn kho gồm những chi phí nào?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Giá gốc hàng tồn kho bao gồm những thành phần chi phí nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ 05.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Giá gốc hàng tồn kho bao gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác phát sinh để có được hàng tồn kho ở địa điểm và trạng thái hiện tại. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ 05.)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Giá gốc hàng tồn kho gồm những chi phí nào?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Giá gốc hàng tồn kho bao gồm những thành phần chi phí nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ 05.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Giá gốc hàng tồn kho bao gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác phát sinh để có được hàng tồn kho ở địa điểm và trạng thái hiện tại. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ 05.)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Giá gốc hàng tồn kho gồm những chi phí nào?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Giá gốc hàng tồn kho bao gồm những thành phần chi phí nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ 05.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Giá gốc hàng tồn kho bao gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác phát sinh để có được hàng tồn kho ở địa điểm và trạng thái hiện tại. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ 05.)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Những chi phí nào không được tính vào giá gốc hàng tồn kho?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Những khoản chi phí nào không được tính vào giá gốc hàng tồn kho trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Các chi phí không được tính vào giá gốc hàng tồn kho gồm: chi phí nguyên liệu, vật liệu, chi phí nhân công và các chi phí sản xuất, kinh doanh khác phát sinh trên mức bình thường; chi phí bảo quản hàng tồn kho, trừ chi phí bảo quản cần thiết cho quá trình sản xuất tiếp theo và chi phí bảo quản quy định ở đoạn 06; chi phí bán hàng; và chi phí quản lý doanh nghiệp. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Những chi phí nào không được tính vào giá gốc hàng tồn kho?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Những khoản chi phí nào không được tính vào giá gốc hàng tồn kho trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Các chi phí không được tính vào giá gốc hàng tồn kho gồm: chi phí nguyên liệu, vật liệu, chi phí nhân công và các chi phí sản xuất, kinh doanh khác phát sinh trên mức bình thường; chi phí bảo quản hàng tồn kho, trừ chi phí bảo quản cần thiết cho quá trình sản xuất tiếp theo và chi phí bảo quản quy định ở đoạn 06; chi phí bán hàng; và chi phí quản lý doanh nghiệp. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Những chi phí nào không được tính vào giá gốc hàng tồn kho?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Những khoản chi phí nào không được tính vào giá gốc hàng tồn kho trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Các chi phí không được tính vào giá gốc hàng tồn kho gồm: chi phí nguyên liệu, vật liệu, chi phí nhân công và các chi phí sản xuất, kinh doanh khác phát sinh trên mức bình thường; chi phí bảo quản hàng tồn kho, trừ chi phí bảo quản cần thiết cho quá trình sản xuất tiếp theo và chi phí bảo quản quy định ở đoạn 06; chi phí bán hàng; và chi phí quản lý doanh nghiệp. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Khi nào một tài sản được ghi nhận là tài sản cố định hữu hình?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Một tài sản cần thỏa mãn những điều kiện nào để được ghi nhận là tài sản cố định hữu hình trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 03 - TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Một tài sản được ghi nhận là tài sản cố định hữu hình khi thỏa mãn đồng thời bốn tiêu chuẩn: chắc chắn thu được lợi ích kinh tế trong tương lai từ việc sử dụng tài sản đó; nguyên giá tài sản được xác định một cách đáng tin cậy; thời gian sử dụng ước tính trên 1 năm; và có đủ tiêu chuẩn giá trị theo quy định hiện hành. (Nguồn: CHUẨN MỰC SỐ 03 - TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Khi nào một tài sản được ghi nhận là tài sản cố định hữu hình?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Một tài sản cần thỏa mãn những điều kiện nào để được ghi nhận là tài sản cố định hữu hình trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 03 - TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Một tài sản được ghi nhận là tài sản cố định hữu hình khi thỏa mãn đồng thời bốn tiêu chuẩn: chắc chắn thu được lợi ích kinh tế trong tương lai từ việc sử dụng tài sản đó; nguyên giá tài sản được xác định một cách đáng tin cậy; thời gian sử dụng ước tính trên 1 năm; và có đủ tiêu chuẩn giá trị theo quy định hiện hành. (Nguồn: CHUẨN MỰC SỐ 03 - TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Khi nào một tài sản được ghi nhận là tài sản cố định hữu hình?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Một tài sản cần thỏa mãn những điều kiện nào để được ghi nhận là tài sản cố định hữu hình trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 03 - TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Một tài sản được ghi nhận là tài sản cố định hữu hình khi thỏa mãn đồng thời bốn tiêu chuẩn: chắc chắn thu được lợi ích kinh tế trong tương lai từ việc sử dụng tài sản đó; nguyên giá tài sản được xác định một cách đáng tin cậy; thời gian sử dụng ước tính trên 1 năm; và có đủ tiêu chuẩn giá trị theo quy định hiện hành. (Nguồn: CHUẨN MỰC SỐ 03 - TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình được hiểu là gì?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình được định nghĩa như thế nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình là tài sản không có hình thái vật chất nhưng xác định được giá trị và do doanh nghiệp nắm giữ, sử dụng trong sản xuất, kinh doanh, cung cấp dịch vụ hoặc cho các đối tượng khác thuê, phù hợp với tiêu chuẩn ghi nhận tài sản cố định vô hình. (Nguồn: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình được hiểu là gì?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình được định nghĩa như thế nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình là tài sản không có hình thái vật chất nhưng xác định được giá trị và do doanh nghiệp nắm giữ, sử dụng trong sản xuất, kinh doanh, cung cấp dịch vụ hoặc cho các đối tượng khác thuê, phù hợp với tiêu chuẩn ghi nhận tài sản cố định vô hình. (Nguồn: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình được hiểu là gì?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình được định nghĩa như thế nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình là tài sản không có hình thái vật chất nhưng xác định được giá trị và do doanh nghiệp nắm giữ, sử dụng trong sản xuất, kinh doanh, cung cấp dịch vụ hoặc cho các đối tượng khác thuê, phù hợp với tiêu chuẩn ghi nhận tài sản cố định vô hình. (Nguồn: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Bất động sản đầu tư là gì?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Bất động sản đầu tư được hiểu là gì trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ QUY ĐỊNH CHUNG ➔ 05.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bất động sản đầu tư là bất động sản, gồm quyền sử dụng đất, nhà, một phần của nhà hoặc cả nhà và đất, cơ sở hạ tầng do chủ sở hữu hoặc người đi thuê tài sản theo hợp đồng thuê tài chính nắm giữ nhằm mục đích thu lợi từ việc cho thuê hoặc chờ tăng giá. Các bất động sản này không nhằm sử dụng trong sản xuất, cung cấp hàng hóa, dịch vụ, mục đích quản lý, hoặc bán trong kỳ hoạt động kinh doanh thông thường. (Nguồn: CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ QUY ĐỊNH CHUNG ➔ 05.)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bất động sản đầu tư là gì?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bất động sản đầu tư được hiểu là gì trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ QUY ĐỊNH CHUNG ➔ 05.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bất động sản đầu tư là bất động sản, gồm quyền sử dụng đất, nhà, một phần của nhà hoặc cả nhà và đất, cơ sở hạ tầng do chủ sở hữu hoặc người đi thuê tài sản theo hợp đồng thuê tài chính nắm giữ nhằm mục đích thu lợi từ việc cho thuê hoặc chờ tăng giá. Các bất động sản này không nhằm sử dụng trong sản xuất, cung cấp hàng hóa, dịch vụ, mục đích quản lý, hoặc bán trong kỳ hoạt động kinh doanh thông thường. (Nguồn: CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ QUY ĐỊNH CHUNG ➔ 05.)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bất động sản đầu tư là gì?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Bất động sản đầu tư được hiểu là gì trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ QUY ĐỊNH CHUNG ➔ 05.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bất động sản đầu tư là bất động sản, gồm quyền sử dụng đất, nhà, một phần của nhà hoặc cả nhà và đất, cơ sở hạ tầng do chủ sở hữu hoặc người đi thuê tài sản theo hợp đồng thuê tài chính nắm giữ nhằm mục đích thu lợi từ việc cho thuê hoặc chờ tăng giá. Các bất động sản này không nhằm sử dụng trong sản xuất, cung cấp hàng hóa, dịch vụ, mục đích quản lý, hoặc bán trong kỳ hoạt động kinh doanh thông thường. (Nguồn: CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ QUY ĐỊNH CHUNG ➔ 05.)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Doanh thu là gì?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Doanh thu được hiểu là gì trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ QUY ĐỊNH CHUNG ➔ 03.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Doanh thu là tổng giá trị các lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán, phát sinh từ các hoạt động sản xuất, kinh doanh thông thường của doanh nghiệp và góp phần làm tăng vốn chủ sở hữu. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ QUY ĐỊNH CHUNG ➔ 03.)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Doanh thu là gì?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Doanh thu được hiểu là gì trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ QUY ĐỊNH CHUNG ➔ 03.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Doanh thu là tổng giá trị các lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán, phát sinh từ các hoạt động sản xuất, kinh doanh thông thường của doanh nghiệp và góp phần làm tăng vốn chủ sở hữu. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ QUY ĐỊNH CHUNG ➔ 03.)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Doanh thu là gì?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Doanh thu được hiểu là gì trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ QUY ĐỊNH CHUNG ➔ 03.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Doanh thu là tổng giá trị các lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán, phát sinh từ các hoạt động sản xuất, kinh doanh thông thường của doanh nghiệp và góp phần làm tăng vốn chủ sở hữu. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ QUY ĐỊNH CHUNG ➔ 03.)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Khi nào doanh thu bán hàng được ghi nhận?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Doanh thu bán hàng được ghi nhận khi thỏa mãn những điều kiện nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Doanh thu bán hàng được ghi nhận khi đồng thời thỏa mãn năm điều kiện: doanh nghiệp đã chuyển giao phần lớn rủi ro và lợi ích gắn liền với quyền sở hữu sản phẩm hoặc hàng hóa cho người mua; không còn nắm giữ quyền quản lý hoặc kiểm soát hàng hóa; doanh thu được xác định tương đối chắc chắn; đã thu được hoặc sẽ thu được lợi ích kinh tế; và xác định được chi phí liên quan đến giao dịch bán hàng. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Khi nào doanh thu bán hàng được ghi nhận?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Doanh thu bán hàng được ghi nhận khi thỏa mãn những điều kiện nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Doanh thu bán hàng được ghi nhận khi đồng thời thỏa mãn năm điều kiện: doanh nghiệp đã chuyển giao phần lớn rủi ro và lợi ích gắn liền với quyền sở hữu sản phẩm hoặc hàng hóa cho người mua; không còn nắm giữ quyền quản lý hoặc kiểm soát hàng hóa; doanh thu được xác định tương đối chắc chắn; đã thu được hoặc sẽ thu được lợi ích kinh tế; và xác định được chi phí liên quan đến giao dịch bán hàng. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Khi nào doanh thu bán hàng được ghi nhận?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Doanh thu bán hàng được ghi nhận khi thỏa mãn những điều kiện nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Doanh thu bán hàng được ghi nhận khi đồng thời thỏa mãn năm điều kiện: doanh nghiệp đã chuyển giao phần lớn rủi ro và lợi ích gắn liền với quyền sở hữu sản phẩm hoặc hàng hóa cho người mua; không còn nắm giữ quyền quản lý hoặc kiểm soát hàng hóa; doanh thu được xác định tương đối chắc chắn; đã thu được hoặc sẽ thu được lợi ích kinh tế; và xác định được chi phí liên quan đến giao dịch bán hàng. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Doanh thu của hợp đồng xây dựng gồm những gì?</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Doanh thu hợp đồng xây dựng bao gồm những khoản nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 15 - HỢP ĐỒNG XÂY DỰNG ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU CỦA HỢP ĐỒNG XÂY DỰNG ➔ 11.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Doanh thu của hợp đồng xây dựng bao gồm doanh thu ban đầu được ghi trong hợp đồng và các khoản tăng, giảm khi thực hiện hợp đồng, các khoản tiền thưởng và các khoản thanh toán khác nếu các khoản này có khả năng làm thay đổi doanh thu và có thể xác định được một cách đáng tin cậy. (Nguồn: CHUẨN MỰC SỐ 15 - HỢP ĐỒNG XÂY DỰNG ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU CỦA HỢP ĐỒNG XÂY DỰNG ➔ 11.)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Doanh thu của hợp đồng xây dựng gồm những gì?</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Doanh thu hợp đồng xây dựng bao gồm những khoản nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 15 - HỢP ĐỒNG XÂY DỰNG ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU CỦA HỢP ĐỒNG XÂY DỰNG ➔ 11.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Doanh thu của hợp đồng xây dựng bao gồm doanh thu ban đầu được ghi trong hợp đồng và các khoản tăng, giảm khi thực hiện hợp đồng, các khoản tiền thưởng và các khoản thanh toán khác nếu các khoản này có khả năng làm thay đổi doanh thu và có thể xác định được một cách đáng tin cậy. (Nguồn: CHUẨN MỰC SỐ 15 - HỢP ĐỒNG XÂY DỰNG ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU CỦA HỢP ĐỒNG XÂY DỰNG ➔ 11.)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Doanh thu của hợp đồng xây dựng gồm những gì?</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Doanh thu hợp đồng xây dựng bao gồm những khoản nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 15 - HỢP ĐỒNG XÂY DỰNG ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU CỦA HỢP ĐỒNG XÂY DỰNG ➔ 11.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Doanh thu của hợp đồng xây dựng bao gồm doanh thu ban đầu được ghi trong hợp đồng và các khoản tăng, giảm khi thực hiện hợp đồng, các khoản tiền thưởng và các khoản thanh toán khác nếu các khoản này có khả năng làm thay đổi doanh thu và có thể xác định được một cách đáng tin cậy. (Nguồn: CHUẨN MỰC SỐ 15 - HỢP ĐỒNG XÂY DỰNG ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU CỦA HỢP ĐỒNG XÂY DỰNG ➔ 11.)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cơ sở dồn tích là gì?</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Cơ sở dồn tích được hiểu như thế nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 01- CHUẨN MỰC CHUNG ➔ NỘI DUNG CHUẨN MỰC ➔ CÁC NGUYÊN TẮC CƠ BẢN ➔ Cơ sở dồn tích ➔ 03.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Theo cơ sở dồn tích, mọi nghiệp vụ kinh tế, tài chính liên quan đến tài sản, nợ phải trả, nguồn vốn chủ sở hữu, doanh thu và chi phí phải được ghi sổ kế toán vào thời điểm phát sinh, không căn cứ vào thời điểm thực tế thu hoặc thực tế chi tiền hay tương đương tiền. Báo cáo tài chính lập trên cơ sở dồn tích phản ánh tình hình tài chính của doanh nghiệp trong quá khứ, hiện tại và tương lai. (Nguồn: CHUẨN MỰC SỐ 01- CHUẨN MỰC CHUNG ➔ NỘI DUNG CHUẨN MỰC ➔ CÁC NGUYÊN TẮC CƠ BẢN ➔ Cơ sở dồn tích ➔ 03.)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Cơ sở dồn tích là gì?</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Cơ sở dồn tích được hiểu như thế nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 01- CHUẨN MỰC CHUNG ➔ NỘI DUNG CHUẨN MỰC ➔ CÁC NGUYÊN TẮC CƠ BẢN ➔ Cơ sở dồn tích ➔ 03.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Theo cơ sở dồn tích, mọi nghiệp vụ kinh tế, tài chính liên quan đến tài sản, nợ phải trả, nguồn vốn chủ sở hữu, doanh thu và chi phí phải được ghi sổ kế toán vào thời điểm phát sinh, không căn cứ vào thời điểm thực tế thu hoặc thực tế chi tiền hay tương đương tiền. Báo cáo tài chính lập trên cơ sở dồn tích phản ánh tình hình tài chính của doanh nghiệp trong quá khứ, hiện tại và tương lai. (Nguồn: CHUẨN MỰC SỐ 01- CHUẨN MỰC CHUNG ➔ NỘI DUNG CHUẨN MỰC ➔ CÁC NGUYÊN TẮC CƠ BẢN ➔ Cơ sở dồn tích ➔ 03.)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Cơ sở dồn tích là gì?</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Cơ sở dồn tích được hiểu như thế nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 01- CHUẨN MỰC CHUNG ➔ NỘI DUNG CHUẨN MỰC ➔ CÁC NGUYÊN TẮC CƠ BẢN ➔ Cơ sở dồn tích ➔ 03.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Theo cơ sở dồn tích, mọi nghiệp vụ kinh tế, tài chính liên quan đến tài sản, nợ phải trả, nguồn vốn chủ sở hữu, doanh thu và chi phí phải được ghi sổ kế toán vào thời điểm phát sinh, không căn cứ vào thời điểm thực tế thu hoặc thực tế chi tiền hay tương đương tiền. Báo cáo tài chính lập trên cơ sở dồn tích phản ánh tình hình tài chính của doanh nghiệp trong quá khứ, hiện tại và tương lai. (Nguồn: CHUẨN MỰC SỐ 01- CHUẨN MỰC CHUNG ➔ NỘI DUNG CHUẨN MỰC ➔ CÁC NGUYÊN TẮC CƠ BẢN ➔ Cơ sở dồn tích ➔ 03.)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Vậy những khoản nào không được đưa vào giá gốc?</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hàng tồn kho là gì?"}, {"role": "assistant", "content": "Hàng tồn kho là những tài sản được giữ để bán, đang trong quá trình sản xuất kinh doanh dở dang, hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ dùng cho sản xuất kinh doanh hoặc cung cấp dịch vụ."}, {"role": "user", "content": "Giá gốc hàng tồn kho gồm những chi phí nào?"}, {"role": "assistant", "content": "Giá gốc hàng tồn kho gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác để có được hàng tồn kho ở địa điểm và trạng thái hiện tại."}, {"role": "user", "content": "Chi phí mua có bao gồm mọi khoản phát sinh khi mua hàng không?"}, {"role": "assistant", "content": "Không phải mọi khoản đều được đưa vào giá gốc; cần phân biệt các khoản được tính vào giá gốc và các khoản bị loại trừ."}]</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Những khoản chi phí nào không được tính vào giá gốc hàng tồn kho trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Các chi phí không được tính vào giá gốc hàng tồn kho gồm: chi phí nguyên liệu, vật liệu, chi phí nhân công và các chi phí sản xuất, kinh doanh khác phát sinh trên mức bình thường; chi phí bảo quản hàng tồn kho, trừ chi phí bảo quản cần thiết cho quá trình sản xuất tiếp theo và chi phí bảo quản quy định ở đoạn 06; chi phí bán hàng; và chi phí quản lý doanh nghiệp. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>11</v>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Vậy những khoản nào không được đưa vào giá gốc?</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hàng tồn kho là gì?"}, {"role": "assistant", "content": "Hàng tồn kho là những tài sản được giữ để bán, đang trong quá trình sản xuất kinh doanh dở dang, hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ dùng cho sản xuất kinh doanh hoặc cung cấp dịch vụ."}, {"role": "user", "content": "Giá gốc hàng tồn kho gồm những chi phí nào?"}, {"role": "assistant", "content": "Giá gốc hàng tồn kho gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác để có được hàng tồn kho ở địa điểm và trạng thái hiện tại."}, {"role": "user", "content": "Chi phí mua có bao gồm mọi khoản phát sinh khi mua hàng không?"}, {"role": "assistant", "content": "Không phải mọi khoản đều được đưa vào giá gốc; cần phân biệt các khoản được tính vào giá gốc và các khoản bị loại trừ."}]</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Những khoản chi phí nào không được tính vào giá gốc hàng tồn kho trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Các chi phí không được tính vào giá gốc hàng tồn kho gồm: chi phí nguyên liệu, vật liệu, chi phí nhân công và các chi phí sản xuất, kinh doanh khác phát sinh trên mức bình thường; chi phí bảo quản hàng tồn kho, trừ chi phí bảo quản cần thiết cho quá trình sản xuất tiếp theo và chi phí bảo quản quy định ở đoạn 06; chi phí bán hàng; và chi phí quản lý doanh nghiệp. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>11</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Vậy những khoản nào không được đưa vào giá gốc?</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hàng tồn kho là gì?"}, {"role": "assistant", "content": "Hàng tồn kho là những tài sản được giữ để bán, đang trong quá trình sản xuất kinh doanh dở dang, hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ dùng cho sản xuất kinh doanh hoặc cung cấp dịch vụ."}, {"role": "user", "content": "Giá gốc hàng tồn kho gồm những chi phí nào?"}, {"role": "assistant", "content": "Giá gốc hàng tồn kho gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác để có được hàng tồn kho ở địa điểm và trạng thái hiện tại."}, {"role": "user", "content": "Chi phí mua có bao gồm mọi khoản phát sinh khi mua hàng không?"}, {"role": "assistant", "content": "Không phải mọi khoản đều được đưa vào giá gốc; cần phân biệt các khoản được tính vào giá gốc và các khoản bị loại trừ."}]</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Những khoản chi phí nào không được tính vào giá gốc hàng tồn kho trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Các chi phí không được tính vào giá gốc hàng tồn kho gồm: chi phí nguyên liệu, vật liệu, chi phí nhân công và các chi phí sản xuất, kinh doanh khác phát sinh trên mức bình thường; chi phí bảo quản hàng tồn kho, trừ chi phí bảo quản cần thiết cho quá trình sản xuất tiếp theo và chi phí bảo quản quy định ở đoạn 06; chi phí bán hàng; và chi phí quản lý doanh nghiệp. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>12</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Nếu thiếu một trong các điều kiện đó thì có ghi nhận được không?</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Doanh thu là gì?"}, {"role": "assistant", "content": "Doanh thu là tổng giá trị các lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán, phát sinh từ hoạt động sản xuất kinh doanh thông thường và góp phần làm tăng vốn chủ sở hữu."}, {"role": "user", "content": "Khi nào doanh thu bán hàng được ghi nhận?"}, {"role": "assistant", "content": "Doanh thu bán hàng được ghi nhận khi đồng thời thỏa mãn năm điều kiện về chuyển giao rủi ro và lợi ích, không còn quyền quản lý hoặc kiểm soát hàng hóa, xác định chắc chắn doanh thu, thu được lợi ích kinh tế và xác định được chi phí liên quan."}]</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Doanh thu bán hàng có được ghi nhận khi chưa thỏa mãn đồng thời các điều kiện ghi nhận doanh thu trong kế toán VAS không?</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Không. Doanh thu bán hàng chỉ được ghi nhận khi đồng thời thỏa mãn tất cả năm điều kiện: đã chuyển giao phần lớn rủi ro và lợi ích gắn với quyền sở hữu cho người mua; không còn nắm giữ quyền quản lý hoặc kiểm soát hàng hóa; doanh thu được xác định tương đối chắc chắn; đã thu được hoặc sẽ thu được lợi ích kinh tế; và xác định được chi phí liên quan đến giao dịch bán hàng. Vì vậy, nếu thiếu một trong các điều kiện này thì chưa đủ cơ sở ghi nhận doanh thu bán hàng. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>12</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Nếu thiếu một trong các điều kiện đó thì có ghi nhận được không?</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Doanh thu là gì?"}, {"role": "assistant", "content": "Doanh thu là tổng giá trị các lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán, phát sinh từ hoạt động sản xuất kinh doanh thông thường và góp phần làm tăng vốn chủ sở hữu."}, {"role": "user", "content": "Khi nào doanh thu bán hàng được ghi nhận?"}, {"role": "assistant", "content": "Doanh thu bán hàng được ghi nhận khi đồng thời thỏa mãn năm điều kiện về chuyển giao rủi ro và lợi ích, không còn quyền quản lý hoặc kiểm soát hàng hóa, xác định chắc chắn doanh thu, thu được lợi ích kinh tế và xác định được chi phí liên quan."}]</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Doanh thu bán hàng có được ghi nhận khi chưa thỏa mãn đồng thời các điều kiện ghi nhận doanh thu trong kế toán VAS không?</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Không. Doanh thu bán hàng chỉ được ghi nhận khi đồng thời thỏa mãn tất cả năm điều kiện: đã chuyển giao phần lớn rủi ro và lợi ích gắn với quyền sở hữu cho người mua; không còn nắm giữ quyền quản lý hoặc kiểm soát hàng hóa; doanh thu được xác định tương đối chắc chắn; đã thu được hoặc sẽ thu được lợi ích kinh tế; và xác định được chi phí liên quan đến giao dịch bán hàng. Vì vậy, nếu thiếu một trong các điều kiện này thì chưa đủ cơ sở ghi nhận doanh thu bán hàng. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>12</v>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Nếu thiếu một trong các điều kiện đó thì có ghi nhận được không?</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Doanh thu là gì?"}, {"role": "assistant", "content": "Doanh thu là tổng giá trị các lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán, phát sinh từ hoạt động sản xuất kinh doanh thông thường và góp phần làm tăng vốn chủ sở hữu."}, {"role": "user", "content": "Khi nào doanh thu bán hàng được ghi nhận?"}, {"role": "assistant", "content": "Doanh thu bán hàng được ghi nhận khi đồng thời thỏa mãn năm điều kiện về chuyển giao rủi ro và lợi ích, không còn quyền quản lý hoặc kiểm soát hàng hóa, xác định chắc chắn doanh thu, thu được lợi ích kinh tế và xác định được chi phí liên quan."}]</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Doanh thu bán hàng có được ghi nhận khi chưa thỏa mãn đồng thời các điều kiện ghi nhận doanh thu trong kế toán VAS không?</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Không. Doanh thu bán hàng chỉ được ghi nhận khi đồng thời thỏa mãn tất cả năm điều kiện: đã chuyển giao phần lớn rủi ro và lợi ích gắn với quyền sở hữu cho người mua; không còn nắm giữ quyền quản lý hoặc kiểm soát hàng hóa; doanh thu được xác định tương đối chắc chắn; đã thu được hoặc sẽ thu được lợi ích kinh tế; và xác định được chi phí liên quan đến giao dịch bán hàng. Vì vậy, nếu thiếu một trong các điều kiện này thì chưa đủ cơ sở ghi nhận doanh thu bán hàng. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>13</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Còn thuê hoạt động thì sao?</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Thuê tài sản là gì?"}, {"role": "assistant", "content": "Thuê tài sản là thỏa thuận giữa bên cho thuê và bên thuê, trong đó bên cho thuê chuyển quyền sử dụng tài sản cho bên thuê trong một khoảng thời gian nhất định để nhận tiền cho thuê."}, {"role": "user", "content": "Thuê tài chính được hiểu thế nào?"}, {"role": "assistant", "content": "Thuê tài chính là thuê tài sản mà bên cho thuê chuyển giao phần lớn rủi ro và lợi ích gắn liền với quyền sở hữu tài sản cho bên thuê."}]</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Thuê hoạt động được hiểu như thế nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ QUY ĐỊNH CHUNG ➔ 04.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Thuê hoạt động là thuê tài sản không phải là thuê tài chính. Trong cùng nhóm thuật ngữ, thuê tài chính được hiểu là thuê tài sản mà bên cho thuê chuyển giao phần lớn rủi ro và lợi ích gắn liền với quyền sở hữu tài sản cho bên thuê. Vì vậy, thuê hoạt động là loại thuê không có đặc điểm chuyển giao phần lớn rủi ro và lợi ích như thuê tài chính. (Nguồn: CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ QUY ĐỊNH CHUNG ➔ 04.)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>13</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Còn thuê hoạt động thì sao?</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Thuê tài sản là gì?"}, {"role": "assistant", "content": "Thuê tài sản là thỏa thuận giữa bên cho thuê và bên thuê, trong đó bên cho thuê chuyển quyền sử dụng tài sản cho bên thuê trong một khoảng thời gian nhất định để nhận tiền cho thuê."}, {"role": "user", "content": "Thuê tài chính được hiểu thế nào?"}, {"role": "assistant", "content": "Thuê tài chính là thuê tài sản mà bên cho thuê chuyển giao phần lớn rủi ro và lợi ích gắn liền với quyền sở hữu tài sản cho bên thuê."}]</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Thuê hoạt động được hiểu như thế nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ QUY ĐỊNH CHUNG ➔ 04.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Thuê hoạt động là thuê tài sản không phải là thuê tài chính. Trong cùng nhóm thuật ngữ, thuê tài chính được hiểu là thuê tài sản mà bên cho thuê chuyển giao phần lớn rủi ro và lợi ích gắn liền với quyền sở hữu tài sản cho bên thuê. Vì vậy, thuê hoạt động là loại thuê không có đặc điểm chuyển giao phần lớn rủi ro và lợi ích như thuê tài chính. (Nguồn: CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ QUY ĐỊNH CHUNG ➔ 04.)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>13</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Còn thuê hoạt động thì sao?</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Thuê tài sản là gì?"}, {"role": "assistant", "content": "Thuê tài sản là thỏa thuận giữa bên cho thuê và bên thuê, trong đó bên cho thuê chuyển quyền sử dụng tài sản cho bên thuê trong một khoảng thời gian nhất định để nhận tiền cho thuê."}, {"role": "user", "content": "Thuê tài chính được hiểu thế nào?"}, {"role": "assistant", "content": "Thuê tài chính là thuê tài sản mà bên cho thuê chuyển giao phần lớn rủi ro và lợi ích gắn liền với quyền sở hữu tài sản cho bên thuê."}]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Thuê hoạt động được hiểu như thế nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ QUY ĐỊNH CHUNG ➔ 04.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Thuê hoạt động là thuê tài sản không phải là thuê tài chính. Trong cùng nhóm thuật ngữ, thuê tài chính được hiểu là thuê tài sản mà bên cho thuê chuyển giao phần lớn rủi ro và lợi ích gắn liền với quyền sở hữu tài sản cho bên thuê. Vì vậy, thuê hoạt động là loại thuê không có đặc điểm chuyển giao phần lớn rủi ro và lợi ích như thuê tài chính. (Nguồn: CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ QUY ĐỊNH CHUNG ➔ 04.)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>14</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Việc thanh toán khoản đó có thể thực hiện bằng cách nào?</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Nợ phải trả là gì?"}, {"role": "assistant", "content": "Nợ phải trả xác định nghĩa vụ hiện tại của doanh nghiệp khi doanh nghiệp nhận về một tài sản, tham gia một cam kết hoặc phát sinh các nghĩa vụ pháp lý."}, {"role": "user", "content": "Nghĩa vụ hiện tại này thường liên quan đến điều gì?"}, {"role": "assistant", "content": "Nó liên quan đến việc doanh nghiệp phải thanh toán hoặc thực hiện một nghĩa vụ phát sinh từ các giao dịch, cam kết hoặc nghĩa vụ pháp lý."}]</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Việc thanh toán các nghĩa vụ hiện tại của doanh nghiệp có thể được thực hiện bằng những cách nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 01- CHUẨN MỰC CHUNG ➔ NỘI DUNG CHUẨN MỰC ➔ CÁC YẾU TỐ CỦA BÁO CÁO TÀI CHÍNH ➔ Nợ phải trả ➔ 27.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Việc thanh toán các nghĩa vụ hiện tại có thể được thực hiện bằng nhiều cách: trả bằng tiền; trả bằng tài sản khác; cung cấp dịch vụ; thay thế nghĩa vụ này bằng nghĩa vụ khác; hoặc chuyển đổi nghĩa vụ nợ phải trả thành vốn chủ sở hữu. (Nguồn: CHUẨN MỰC SỐ 01- CHUẨN MỰC CHUNG ➔ NỘI DUNG CHUẨN MỰC ➔ CÁC YẾU TỐ CỦA BÁO CÁO TÀI CHÍNH ➔ Nợ phải trả ➔ 27.)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>14</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Việc thanh toán khoản đó có thể thực hiện bằng cách nào?</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Nợ phải trả là gì?"}, {"role": "assistant", "content": "Nợ phải trả xác định nghĩa vụ hiện tại của doanh nghiệp khi doanh nghiệp nhận về một tài sản, tham gia một cam kết hoặc phát sinh các nghĩa vụ pháp lý."}, {"role": "user", "content": "Nghĩa vụ hiện tại này thường liên quan đến điều gì?"}, {"role": "assistant", "content": "Nó liên quan đến việc doanh nghiệp phải thanh toán hoặc thực hiện một nghĩa vụ phát sinh từ các giao dịch, cam kết hoặc nghĩa vụ pháp lý."}]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Việc thanh toán các nghĩa vụ hiện tại của doanh nghiệp có thể được thực hiện bằng những cách nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 01- CHUẨN MỰC CHUNG ➔ NỘI DUNG CHUẨN MỰC ➔ CÁC YẾU TỐ CỦA BÁO CÁO TÀI CHÍNH ➔ Nợ phải trả ➔ 27.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Việc thanh toán các nghĩa vụ hiện tại có thể được thực hiện bằng nhiều cách: trả bằng tiền; trả bằng tài sản khác; cung cấp dịch vụ; thay thế nghĩa vụ này bằng nghĩa vụ khác; hoặc chuyển đổi nghĩa vụ nợ phải trả thành vốn chủ sở hữu. (Nguồn: CHUẨN MỰC SỐ 01- CHUẨN MỰC CHUNG ➔ NỘI DUNG CHUẨN MỰC ➔ CÁC YẾU TỐ CỦA BÁO CÁO TÀI CHÍNH ➔ Nợ phải trả ➔ 27.)</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>14</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Việc thanh toán khoản đó có thể thực hiện bằng cách nào?</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Nợ phải trả là gì?"}, {"role": "assistant", "content": "Nợ phải trả xác định nghĩa vụ hiện tại của doanh nghiệp khi doanh nghiệp nhận về một tài sản, tham gia một cam kết hoặc phát sinh các nghĩa vụ pháp lý."}, {"role": "user", "content": "Nghĩa vụ hiện tại này thường liên quan đến điều gì?"}, {"role": "assistant", "content": "Nó liên quan đến việc doanh nghiệp phải thanh toán hoặc thực hiện một nghĩa vụ phát sinh từ các giao dịch, cam kết hoặc nghĩa vụ pháp lý."}]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Việc thanh toán các nghĩa vụ hiện tại của doanh nghiệp có thể được thực hiện bằng những cách nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 01- CHUẨN MỰC CHUNG ➔ NỘI DUNG CHUẨN MỰC ➔ CÁC YẾU TỐ CỦA BÁO CÁO TÀI CHÍNH ➔ Nợ phải trả ➔ 27.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Việc thanh toán các nghĩa vụ hiện tại có thể được thực hiện bằng nhiều cách: trả bằng tiền; trả bằng tài sản khác; cung cấp dịch vụ; thay thế nghĩa vụ này bằng nghĩa vụ khác; hoặc chuyển đổi nghĩa vụ nợ phải trả thành vốn chủ sở hữu. (Nguồn: CHUẨN MỰC SỐ 01- CHUẨN MỰC CHUNG ➔ NỘI DUNG CHUẨN MỰC ➔ CÁC YẾU TỐ CỦA BÁO CÁO TÀI CHÍNH ➔ Nợ phải trả ➔ 27.)</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>15</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Vậy giá trị thanh lý của tài sản đó được xác định khi nào?</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định vô hình được hiểu là gì?"}, {"role": "assistant", "content": "Tài sản cố định vô hình là tài sản không có hình thái vật chất nhưng xác định được giá trị và do doanh nghiệp nắm giữ, sử dụng trong sản xuất kinh doanh, cung cấp dịch vụ hoặc cho thuê."}, {"role": "user", "content": "Nó có phải khấu hao trong thời gian sử dụng không?"}, {"role": "assistant", "content": "Có. Giá trị phải khấu hao của tài sản cố định vô hình được phân bổ có hệ thống trong suốt thời gian sử dụng hữu ích của tài sản."}, {"role": "user", "content": "Khi tính khấu hao thì có xét đến giá trị còn lại cuối thời gian sử dụng không?"}, {"role": "assistant", "content": "Có thể có, nhưng cần xem tài sản cố định vô hình đó có giá trị thanh lý theo điều kiện của VAS hay không."}]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình có giá trị thanh lý khi nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ GIÁ TRỊ THANH LÝ ➔ 62.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình có giá trị thanh lý khi có bên thứ ba thỏa thuận mua lại tài sản đó vào cuối thời gian sử dụng hữu ích, hoặc có thị trường hoạt động vào cuối thời gian sử dụng hữu ích và giá trị thanh lý có thể được xác định thông qua giá thị trường. Nếu không có một trong hai điều kiện này thì giá trị thanh lý của tài sản cố định vô hình được xác định bằng không (0). (Nguồn: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ GIÁ TRỊ THANH LÝ ➔ 62.)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>15</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Vậy giá trị thanh lý của tài sản đó được xác định khi nào?</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định vô hình được hiểu là gì?"}, {"role": "assistant", "content": "Tài sản cố định vô hình là tài sản không có hình thái vật chất nhưng xác định được giá trị và do doanh nghiệp nắm giữ, sử dụng trong sản xuất kinh doanh, cung cấp dịch vụ hoặc cho thuê."}, {"role": "user", "content": "Nó có phải khấu hao trong thời gian sử dụng không?"}, {"role": "assistant", "content": "Có. Giá trị phải khấu hao của tài sản cố định vô hình được phân bổ có hệ thống trong suốt thời gian sử dụng hữu ích của tài sản."}, {"role": "user", "content": "Khi tính khấu hao thì có xét đến giá trị còn lại cuối thời gian sử dụng không?"}, {"role": "assistant", "content": "Có thể có, nhưng cần xem tài sản cố định vô hình đó có giá trị thanh lý theo điều kiện của VAS hay không."}]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình có giá trị thanh lý khi nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ GIÁ TRỊ THANH LÝ ➔ 62.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình có giá trị thanh lý khi có bên thứ ba thỏa thuận mua lại tài sản đó vào cuối thời gian sử dụng hữu ích, hoặc có thị trường hoạt động vào cuối thời gian sử dụng hữu ích và giá trị thanh lý có thể được xác định thông qua giá thị trường. Nếu không có một trong hai điều kiện này thì giá trị thanh lý của tài sản cố định vô hình được xác định bằng không (0). (Nguồn: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ GIÁ TRỊ THANH LÝ ➔ 62.)</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>15</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Vậy giá trị thanh lý của tài sản đó được xác định khi nào?</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định vô hình được hiểu là gì?"}, {"role": "assistant", "content": "Tài sản cố định vô hình là tài sản không có hình thái vật chất nhưng xác định được giá trị và do doanh nghiệp nắm giữ, sử dụng trong sản xuất kinh doanh, cung cấp dịch vụ hoặc cho thuê."}, {"role": "user", "content": "Nó có phải khấu hao trong thời gian sử dụng không?"}, {"role": "assistant", "content": "Có. Giá trị phải khấu hao của tài sản cố định vô hình được phân bổ có hệ thống trong suốt thời gian sử dụng hữu ích của tài sản."}, {"role": "user", "content": "Khi tính khấu hao thì có xét đến giá trị còn lại cuối thời gian sử dụng không?"}, {"role": "assistant", "content": "Có thể có, nhưng cần xem tài sản cố định vô hình đó có giá trị thanh lý theo điều kiện của VAS hay không."}]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình có giá trị thanh lý khi nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ GIÁ TRỊ THANH LÝ ➔ 62.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tài sản cố định vô hình có giá trị thanh lý khi có bên thứ ba thỏa thuận mua lại tài sản đó vào cuối thời gian sử dụng hữu ích, hoặc có thị trường hoạt động vào cuối thời gian sử dụng hữu ích và giá trị thanh lý có thể được xác định thông qua giá thị trường. Nếu không có một trong hai điều kiện này thì giá trị thanh lý của tài sản cố định vô hình được xác định bằng không (0). (Nguồn: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ GIÁ TRỊ THANH LÝ ➔ 62.)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>16</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Vậy để ghi nhận thì nó phải đáp ứng những tiêu chuẩn nào?</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định hữu hình được hiểu là gì?"}, {"role": "assistant", "content": "Tài sản cố định hữu hình là tài sản có hình thái vật chất do doanh nghiệp nắm giữ để sử dụng cho hoạt động sản xuất, kinh doanh và phải phù hợp với tiêu chuẩn ghi nhận tài sản cố định hữu hình."}, {"role": "user", "content": "Ví dụ như máy móc hoặc phương tiện vận tải thì thuộc nhóm này không?"}, {"role": "assistant", "content": "Có. Tài sản cố định hữu hình có thể gồm nhà cửa, vật kiến trúc, máy móc thiết bị, phương tiện vận tải, thiết bị truyền dẫn, thiết bị dụng cụ quản lý và các tài sản hữu hình khác."}, {"role": "user", "content": "Nếu doanh nghiệp muốn ghi nhận một tài sản vào nhóm này thì cần xem xét gì?"}, {"role": "assistant", "content": "Cần xem tài sản đó có đáp ứng đầy đủ các tiêu chuẩn ghi nhận tài sản cố định hữu hình theo VAS hay không."}]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Tài sản cố định hữu hình cần đáp ứng những tiêu chuẩn nào để được ghi nhận trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 03 - TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ NỘI DUNG CHUẨN MỰC GHI NHẬN TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tài sản được ghi nhận là tài sản cố định hữu hình khi thỏa mãn đồng thời bốn tiêu chuẩn: chắc chắn thu được lợi ích kinh tế trong tương lai từ việc sử dụng tài sản đó; nguyên giá tài sản được xác định một cách đáng tin cậy; thời gian sử dụng ước tính trên 1 năm; và có đủ tiêu chuẩn giá trị theo quy định hiện hành. (Nguồn: CHUẨN MỰC SỐ 03 - TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ NỘI DUNG CHUẨN MỰC GHI NHẬN TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>16</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Vậy để ghi nhận thì nó phải đáp ứng những tiêu chuẩn nào?</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định hữu hình được hiểu là gì?"}, {"role": "assistant", "content": "Tài sản cố định hữu hình là tài sản có hình thái vật chất do doanh nghiệp nắm giữ để sử dụng cho hoạt động sản xuất, kinh doanh và phải phù hợp với tiêu chuẩn ghi nhận tài sản cố định hữu hình."}, {"role": "user", "content": "Ví dụ như máy móc hoặc phương tiện vận tải thì thuộc nhóm này không?"}, {"role": "assistant", "content": "Có. Tài sản cố định hữu hình có thể gồm nhà cửa, vật kiến trúc, máy móc thiết bị, phương tiện vận tải, thiết bị truyền dẫn, thiết bị dụng cụ quản lý và các tài sản hữu hình khác."}, {"role": "user", "content": "Nếu doanh nghiệp muốn ghi nhận một tài sản vào nhóm này thì cần xem xét gì?"}, {"role": "assistant", "content": "Cần xem tài sản đó có đáp ứng đầy đủ các tiêu chuẩn ghi nhận tài sản cố định hữu hình theo VAS hay không."}]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Tài sản cố định hữu hình cần đáp ứng những tiêu chuẩn nào để được ghi nhận trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 03 - TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ NỘI DUNG CHUẨN MỰC GHI NHẬN TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tài sản được ghi nhận là tài sản cố định hữu hình khi thỏa mãn đồng thời bốn tiêu chuẩn: chắc chắn thu được lợi ích kinh tế trong tương lai từ việc sử dụng tài sản đó; nguyên giá tài sản được xác định một cách đáng tin cậy; thời gian sử dụng ước tính trên 1 năm; và có đủ tiêu chuẩn giá trị theo quy định hiện hành. (Nguồn: CHUẨN MỰC SỐ 03 - TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ NỘI DUNG CHUẨN MỰC GHI NHẬN TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>16</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Vậy để ghi nhận thì nó phải đáp ứng những tiêu chuẩn nào?</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định hữu hình được hiểu là gì?"}, {"role": "assistant", "content": "Tài sản cố định hữu hình là tài sản có hình thái vật chất do doanh nghiệp nắm giữ để sử dụng cho hoạt động sản xuất, kinh doanh và phải phù hợp với tiêu chuẩn ghi nhận tài sản cố định hữu hình."}, {"role": "user", "content": "Ví dụ như máy móc hoặc phương tiện vận tải thì thuộc nhóm này không?"}, {"role": "assistant", "content": "Có. Tài sản cố định hữu hình có thể gồm nhà cửa, vật kiến trúc, máy móc thiết bị, phương tiện vận tải, thiết bị truyền dẫn, thiết bị dụng cụ quản lý và các tài sản hữu hình khác."}, {"role": "user", "content": "Nếu doanh nghiệp muốn ghi nhận một tài sản vào nhóm này thì cần xem xét gì?"}, {"role": "assistant", "content": "Cần xem tài sản đó có đáp ứng đầy đủ các tiêu chuẩn ghi nhận tài sản cố định hữu hình theo VAS hay không."}]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Tài sản cố định hữu hình cần đáp ứng những tiêu chuẩn nào để được ghi nhận trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 03 - TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ NỘI DUNG CHUẨN MỰC GHI NHẬN TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tài sản được ghi nhận là tài sản cố định hữu hình khi thỏa mãn đồng thời bốn tiêu chuẩn: chắc chắn thu được lợi ích kinh tế trong tương lai từ việc sử dụng tài sản đó; nguyên giá tài sản được xác định một cách đáng tin cậy; thời gian sử dụng ước tính trên 1 năm; và có đủ tiêu chuẩn giá trị theo quy định hiện hành. (Nguồn: CHUẨN MỰC SỐ 03 - TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ NỘI DUNG CHUẨN MỰC GHI NHẬN TÀI SẢN CỐ ĐỊNH HỮU HÌNH ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>17</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Vậy có những phương pháp tính nào?</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hàng tồn kho là gì?"}, {"role": "assistant", "content": "Hàng tồn kho là tài sản được giữ để bán, đang trong quá trình sản xuất kinh doanh dở dang, hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ dùng cho sản xuất kinh doanh hoặc cung cấp dịch vụ."}, {"role": "user", "content": "Khi ghi nhận hàng tồn kho thì cần xác định giá trị của nó đúng không?"}, {"role": "assistant", "content": "Đúng. Hàng tồn kho cần được xác định giá trị để ghi sổ kế toán và lập báo cáo tài chính."}]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Giá trị hàng tồn kho được tính theo những phương pháp nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 13.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Việc tính giá trị hàng tồn kho được áp dụng theo một trong các phương pháp: phương pháp tính theo giá đích danh; phương pháp bình quân gia quyền; phương pháp nhập trước, xuất trước; và phương pháp nhập sau, xuất trước. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 13.)</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>17</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Vậy có những phương pháp tính nào?</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hàng tồn kho là gì?"}, {"role": "assistant", "content": "Hàng tồn kho là tài sản được giữ để bán, đang trong quá trình sản xuất kinh doanh dở dang, hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ dùng cho sản xuất kinh doanh hoặc cung cấp dịch vụ."}, {"role": "user", "content": "Khi ghi nhận hàng tồn kho thì cần xác định giá trị của nó đúng không?"}, {"role": "assistant", "content": "Đúng. Hàng tồn kho cần được xác định giá trị để ghi sổ kế toán và lập báo cáo tài chính."}]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Giá trị hàng tồn kho được tính theo những phương pháp nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 13.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Việc tính giá trị hàng tồn kho được áp dụng theo một trong các phương pháp: phương pháp tính theo giá đích danh; phương pháp bình quân gia quyền; phương pháp nhập trước, xuất trước; và phương pháp nhập sau, xuất trước. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 13.)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>17</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Vậy có những phương pháp tính nào?</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hàng tồn kho là gì?"}, {"role": "assistant", "content": "Hàng tồn kho là tài sản được giữ để bán, đang trong quá trình sản xuất kinh doanh dở dang, hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ dùng cho sản xuất kinh doanh hoặc cung cấp dịch vụ."}, {"role": "user", "content": "Khi ghi nhận hàng tồn kho thì cần xác định giá trị của nó đúng không?"}, {"role": "assistant", "content": "Đúng. Hàng tồn kho cần được xác định giá trị để ghi sổ kế toán và lập báo cáo tài chính."}]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Giá trị hàng tồn kho được tính theo những phương pháp nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 13.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Việc tính giá trị hàng tồn kho được áp dụng theo một trong các phương pháp: phương pháp tính theo giá đích danh; phương pháp bình quân gia quyền; phương pháp nhập trước, xuất trước; và phương pháp nhập sau, xuất trước. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 13.)</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>18</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Chi phí đó bao gồm những khoản nào?</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Giá gốc hàng tồn kho gồm những chi phí nào?"}, {"role": "assistant", "content": "Giá gốc hàng tồn kho bao gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác để có được hàng tồn kho ở địa điểm và trạng thái hiện tại."}, {"role": "user", "content": "Tôi muốn hiểu rõ hơn về phần chi phí mua."}, {"role": "assistant", "content": "Chi phí mua là một thành phần của giá gốc hàng tồn kho và cần xác định các khoản được tính trực tiếp vào chi phí mua."}]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Chi phí mua của hàng tồn kho bao gồm những khoản nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí mua ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Chi phí mua của hàng tồn kho bao gồm giá mua, các loại thuế không được hoàn lại, chi phí vận chuyển, bốc xếp, bảo quản trong quá trình mua hàng và các chi phí khác có liên quan trực tiếp đến việc mua hàng tồn kho. Các khoản chiết khấu thương mại và giảm giá hàng mua do hàng mua không đúng quy cách, phẩm chất được trừ khỏi chi phí mua. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí mua ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>18</v>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Chi phí đó bao gồm những khoản nào?</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Giá gốc hàng tồn kho gồm những chi phí nào?"}, {"role": "assistant", "content": "Giá gốc hàng tồn kho bao gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác để có được hàng tồn kho ở địa điểm và trạng thái hiện tại."}, {"role": "user", "content": "Tôi muốn hiểu rõ hơn về phần chi phí mua."}, {"role": "assistant", "content": "Chi phí mua là một thành phần của giá gốc hàng tồn kho và cần xác định các khoản được tính trực tiếp vào chi phí mua."}]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Chi phí mua của hàng tồn kho bao gồm những khoản nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí mua ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Chi phí mua của hàng tồn kho bao gồm giá mua, các loại thuế không được hoàn lại, chi phí vận chuyển, bốc xếp, bảo quản trong quá trình mua hàng và các chi phí khác có liên quan trực tiếp đến việc mua hàng tồn kho. Các khoản chiết khấu thương mại và giảm giá hàng mua do hàng mua không đúng quy cách, phẩm chất được trừ khỏi chi phí mua. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí mua ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>18</v>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Chi phí đó bao gồm những khoản nào?</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Giá gốc hàng tồn kho gồm những chi phí nào?"}, {"role": "assistant", "content": "Giá gốc hàng tồn kho bao gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác để có được hàng tồn kho ở địa điểm và trạng thái hiện tại."}, {"role": "user", "content": "Tôi muốn hiểu rõ hơn về phần chi phí mua."}, {"role": "assistant", "content": "Chi phí mua là một thành phần của giá gốc hàng tồn kho và cần xác định các khoản được tính trực tiếp vào chi phí mua."}]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Chi phí mua của hàng tồn kho bao gồm những khoản nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí mua ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Chi phí mua của hàng tồn kho bao gồm giá mua, các loại thuế không được hoàn lại, chi phí vận chuyển, bốc xếp, bảo quản trong quá trình mua hàng và các chi phí khác có liên quan trực tiếp đến việc mua hàng tồn kho. Các khoản chiết khấu thương mại và giảm giá hàng mua do hàng mua không đúng quy cách, phẩm chất được trừ khỏi chi phí mua. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí mua ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>19</v>
+      </c>
+      <c r="B56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Hai bên phải xác định việc đó vào lúc nào?</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Thuê tài sản là gì?"}, {"role": "assistant", "content": "Thuê tài sản là thỏa thuận giữa bên cho thuê và bên thuê, trong đó bên cho thuê chuyển quyền sử dụng tài sản cho bên thuê trong một thời gian nhất định để nhận tiền cho thuê."}, {"role": "user", "content": "Trong thuê tài sản có những loại nào?"}, {"role": "assistant", "content": "Trong VAS, thuê tài sản được phân loại thành thuê tài chính hoặc thuê hoạt động."}, {"role": "user", "content": "Việc phân loại này có quan trọng với cả bên cho thuê và bên thuê không?"}, {"role": "assistant", "content": "Có. Cả bên cho thuê và bên thuê đều cần xác định hợp đồng thuê thuộc loại thuê tài chính hay thuê hoạt động."}]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Bên cho thuê và bên thuê phải xác định loại thuê tài sản vào thời điểm nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 08.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Bên cho thuê và bên thuê phải xác định thuê tài sản là thuê tài chính hay thuê hoạt động ngay tại thời điểm khởi đầu thuê tài sản. (Nguồn: CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 08.)</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>19</v>
+      </c>
+      <c r="B57" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Hai bên phải xác định việc đó vào lúc nào?</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Thuê tài sản là gì?"}, {"role": "assistant", "content": "Thuê tài sản là thỏa thuận giữa bên cho thuê và bên thuê, trong đó bên cho thuê chuyển quyền sử dụng tài sản cho bên thuê trong một thời gian nhất định để nhận tiền cho thuê."}, {"role": "user", "content": "Trong thuê tài sản có những loại nào?"}, {"role": "assistant", "content": "Trong VAS, thuê tài sản được phân loại thành thuê tài chính hoặc thuê hoạt động."}, {"role": "user", "content": "Việc phân loại này có quan trọng với cả bên cho thuê và bên thuê không?"}, {"role": "assistant", "content": "Có. Cả bên cho thuê và bên thuê đều cần xác định hợp đồng thuê thuộc loại thuê tài chính hay thuê hoạt động."}]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Bên cho thuê và bên thuê phải xác định loại thuê tài sản vào thời điểm nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 08.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bên cho thuê và bên thuê phải xác định thuê tài sản là thuê tài chính hay thuê hoạt động ngay tại thời điểm khởi đầu thuê tài sản. (Nguồn: CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 08.)</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>19</v>
+      </c>
+      <c r="B58" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Hai bên phải xác định việc đó vào lúc nào?</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Thuê tài sản là gì?"}, {"role": "assistant", "content": "Thuê tài sản là thỏa thuận giữa bên cho thuê và bên thuê, trong đó bên cho thuê chuyển quyền sử dụng tài sản cho bên thuê trong một thời gian nhất định để nhận tiền cho thuê."}, {"role": "user", "content": "Trong thuê tài sản có những loại nào?"}, {"role": "assistant", "content": "Trong VAS, thuê tài sản được phân loại thành thuê tài chính hoặc thuê hoạt động."}, {"role": "user", "content": "Việc phân loại này có quan trọng với cả bên cho thuê và bên thuê không?"}, {"role": "assistant", "content": "Có. Cả bên cho thuê và bên thuê đều cần xác định hợp đồng thuê thuộc loại thuê tài chính hay thuê hoạt động."}]</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Bên cho thuê và bên thuê phải xác định loại thuê tài sản vào thời điểm nào trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 08.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bên cho thuê và bên thuê phải xác định thuê tài sản là thuê tài chính hay thuê hoạt động ngay tại thời điểm khởi đầu thuê tài sản. (Nguồn: CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 08.)</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>20</v>
+      </c>
+      <c r="B59" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Việc phân loại đó dựa vào yếu tố nào?</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Thuê tài sản là gì?"}, {"role": "assistant", "content": "Thuê tài sản là thỏa thuận trong đó bên cho thuê chuyển quyền sử dụng tài sản cho bên thuê trong một thời gian nhất định để nhận tiền cho thuê."}, {"role": "user", "content": "Trong VAS có thuê tài chính và thuê hoạt động đúng không?"}, {"role": "assistant", "content": "Đúng. Thuê tài sản được phân loại thành thuê tài chính hoặc thuê hoạt động."}, {"role": "user", "content": "Hai loại đó cần được xác định ở thời điểm nào?"}, {"role": "assistant", "content": "Bên cho thuê và bên thuê phải xác định thuê tài sản là thuê tài chính hay thuê hoạt động ngay tại thời điểm khởi đầu thuê tài sản."}]</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Việc phân loại thuê tài sản trong kế toán VAS dựa vào yếu tố nào?</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Việc phân loại thuê tài sản được căn cứ vào mức độ chuyển giao các rủi ro và lợi ích gắn liền với quyền sở hữu tài sản thuê từ bên cho thuê cho bên thuê. Rủi ro gồm khả năng thiệt hại do không tận dụng hết năng lực sản xuất, lạc hậu kỹ thuật và biến động bất lợi của tình hình kinh tế ảnh hưởng đến khả năng thu hồi vốn. Lợi ích gồm lợi nhuận ước tính từ hoạt động của tài sản thuê trong thời gian sử dụng kinh tế và thu nhập ước tính từ sự gia tăng giá trị tài sản hoặc giá trị thanh lý có thể thu hồi. (Nguồn: CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>20</v>
+      </c>
+      <c r="B60" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Việc phân loại đó dựa vào yếu tố nào?</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Thuê tài sản là gì?"}, {"role": "assistant", "content": "Thuê tài sản là thỏa thuận trong đó bên cho thuê chuyển quyền sử dụng tài sản cho bên thuê trong một thời gian nhất định để nhận tiền cho thuê."}, {"role": "user", "content": "Trong VAS có thuê tài chính và thuê hoạt động đúng không?"}, {"role": "assistant", "content": "Đúng. Thuê tài sản được phân loại thành thuê tài chính hoặc thuê hoạt động."}, {"role": "user", "content": "Hai loại đó cần được xác định ở thời điểm nào?"}, {"role": "assistant", "content": "Bên cho thuê và bên thuê phải xác định thuê tài sản là thuê tài chính hay thuê hoạt động ngay tại thời điểm khởi đầu thuê tài sản."}]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Việc phân loại thuê tài sản trong kế toán VAS dựa vào yếu tố nào?</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Việc phân loại thuê tài sản được căn cứ vào mức độ chuyển giao các rủi ro và lợi ích gắn liền với quyền sở hữu tài sản thuê từ bên cho thuê cho bên thuê. Rủi ro gồm khả năng thiệt hại do không tận dụng hết năng lực sản xuất, lạc hậu kỹ thuật và biến động bất lợi của tình hình kinh tế ảnh hưởng đến khả năng thu hồi vốn. Lợi ích gồm lợi nhuận ước tính từ hoạt động của tài sản thuê trong thời gian sử dụng kinh tế và thu nhập ước tính từ sự gia tăng giá trị tài sản hoặc giá trị thanh lý có thể thu hồi. (Nguồn: CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>20</v>
+      </c>
+      <c r="B61" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Việc phân loại đó dựa vào yếu tố nào?</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Thuê tài sản là gì?"}, {"role": "assistant", "content": "Thuê tài sản là thỏa thuận trong đó bên cho thuê chuyển quyền sử dụng tài sản cho bên thuê trong một thời gian nhất định để nhận tiền cho thuê."}, {"role": "user", "content": "Trong VAS có thuê tài chính và thuê hoạt động đúng không?"}, {"role": "assistant", "content": "Đúng. Thuê tài sản được phân loại thành thuê tài chính hoặc thuê hoạt động."}, {"role": "user", "content": "Hai loại đó cần được xác định ở thời điểm nào?"}, {"role": "assistant", "content": "Bên cho thuê và bên thuê phải xác định thuê tài sản là thuê tài chính hay thuê hoạt động ngay tại thời điểm khởi đầu thuê tài sản."}]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Việc phân loại thuê tài sản trong kế toán VAS dựa vào yếu tố nào?</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Việc phân loại thuê tài sản được căn cứ vào mức độ chuyển giao các rủi ro và lợi ích gắn liền với quyền sở hữu tài sản thuê từ bên cho thuê cho bên thuê. Rủi ro gồm khả năng thiệt hại do không tận dụng hết năng lực sản xuất, lạc hậu kỹ thuật và biến động bất lợi của tình hình kinh tế ảnh hưởng đến khả năng thu hồi vốn. Lợi ích gồm lợi nhuận ước tính từ hoạt động của tài sản thuê trong thời gian sử dụng kinh tế và thu nhập ước tính từ sự gia tăng giá trị tài sản hoặc giá trị thanh lý có thể thu hồi. (Nguồn: CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>21</v>
+      </c>
+      <c r="B62" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Vậy Bitcoin có được ghi nhận là hàng tồn kho theo cách này không?</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hàng tồn kho là gì?"}, {"role": "assistant", "content": "Hàng tồn kho là tài sản được giữ để bán, đang trong quá trình sản xuất kinh doanh dở dang, hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ dùng cho sản xuất kinh doanh hoặc cung cấp dịch vụ."}, {"role": "user", "content": "Giá gốc hàng tồn kho gồm những chi phí nào?"}, {"role": "assistant", "content": "Giá gốc hàng tồn kho gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác để có được hàng tồn kho ở địa điểm và trạng thái hiện tại."}]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Bitcoin có được ghi nhận là hàng tồn kho theo kế toán VAS không?</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 03.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để kết luận Bitcoin được ghi nhận là hàng tồn kho theo tài liệu VAS hiện có. Đoạn nguồn chỉ định nghĩa hàng tồn kho là tài sản được giữ để bán trong kỳ sản xuất, kinh doanh bình thường; đang trong quá trình sản xuất, kinh doanh dở dang; hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ để sử dụng trong sản xuất, kinh doanh hoặc cung cấp dịch vụ. Tài liệu không đề cập đến Bitcoin hay tiền điện tử, nên không nên suy diễn cách ghi nhận Bitcoin từ quy định này. (Nguồn liên quan về phạm vi hàng tồn kho: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 03.)</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>21</v>
+      </c>
+      <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Vậy Bitcoin có được ghi nhận là hàng tồn kho theo cách này không?</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hàng tồn kho là gì?"}, {"role": "assistant", "content": "Hàng tồn kho là tài sản được giữ để bán, đang trong quá trình sản xuất kinh doanh dở dang, hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ dùng cho sản xuất kinh doanh hoặc cung cấp dịch vụ."}, {"role": "user", "content": "Giá gốc hàng tồn kho gồm những chi phí nào?"}, {"role": "assistant", "content": "Giá gốc hàng tồn kho gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác để có được hàng tồn kho ở địa điểm và trạng thái hiện tại."}]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Bitcoin có được ghi nhận là hàng tồn kho theo kế toán VAS không?</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 03.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để kết luận Bitcoin được ghi nhận là hàng tồn kho theo tài liệu VAS hiện có. Đoạn nguồn chỉ định nghĩa hàng tồn kho là tài sản được giữ để bán trong kỳ sản xuất, kinh doanh bình thường; đang trong quá trình sản xuất, kinh doanh dở dang; hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ để sử dụng trong sản xuất, kinh doanh hoặc cung cấp dịch vụ. Tài liệu không đề cập đến Bitcoin hay tiền điện tử, nên không nên suy diễn cách ghi nhận Bitcoin từ quy định này. (Nguồn liên quan về phạm vi hàng tồn kho: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 03.)</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>21</v>
+      </c>
+      <c r="B64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Vậy Bitcoin có được ghi nhận là hàng tồn kho theo cách này không?</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hàng tồn kho là gì?"}, {"role": "assistant", "content": "Hàng tồn kho là tài sản được giữ để bán, đang trong quá trình sản xuất kinh doanh dở dang, hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ dùng cho sản xuất kinh doanh hoặc cung cấp dịch vụ."}, {"role": "user", "content": "Giá gốc hàng tồn kho gồm những chi phí nào?"}, {"role": "assistant", "content": "Giá gốc hàng tồn kho gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác để có được hàng tồn kho ở địa điểm và trạng thái hiện tại."}]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Bitcoin có được ghi nhận là hàng tồn kho theo kế toán VAS không?</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 03.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để kết luận Bitcoin được ghi nhận là hàng tồn kho theo tài liệu VAS hiện có. Đoạn nguồn chỉ định nghĩa hàng tồn kho là tài sản được giữ để bán trong kỳ sản xuất, kinh doanh bình thường; đang trong quá trình sản xuất, kinh doanh dở dang; hoặc là nguyên liệu, vật liệu, công cụ, dụng cụ để sử dụng trong sản xuất, kinh doanh hoặc cung cấp dịch vụ. Tài liệu không đề cập đến Bitcoin hay tiền điện tử, nên không nên suy diễn cách ghi nhận Bitcoin từ quy định này. (Nguồn liên quan về phạm vi hàng tồn kho: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ QUY ĐỊNH CHUNG ➔ 03.)</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>22</v>
+      </c>
+      <c r="B65" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Vậy chuẩn mực này có quy định mức lương tối thiểu cho nhân viên không?</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Chi phí mua của hàng tồn kho gồm những khoản nào?"}, {"role": "assistant", "content": "Chi phí mua của hàng tồn kho gồm giá mua, thuế không được hoàn lại, chi phí vận chuyển, bốc xếp, bảo quản trong quá trình mua hàng và các chi phí liên quan trực tiếp khác."}, {"role": "user", "content": "Còn chi phí nhân công thì có liên quan đến hàng tồn kho không?"}, {"role": "assistant", "content": "Có thể có trong chi phí chế biến hàng tồn kho, ví dụ chi phí nhân công trực tiếp liên quan đến sản phẩm sản xuất."}]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>VAS về hàng tồn kho có quy định mức lương tối thiểu cho nhân viên không?</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này bị lệch phạm vi của tài liệu VAS về hàng tồn kho. Các đoạn liên quan trong tài liệu chỉ nói về cách xác định giá trị hàng tồn kho, chi phí mua, chi phí chế biến và các khoản chi phí được hoặc không được tính vào giá gốc hàng tồn kho. Tài liệu không quy định mức lương tối thiểu cho nhân viên, nên không có căn cứ để trả lời mức lương tối thiểu từ bộ tài liệu này.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>22</v>
+      </c>
+      <c r="B66" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Vậy chuẩn mực này có quy định mức lương tối thiểu cho nhân viên không?</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Chi phí mua của hàng tồn kho gồm những khoản nào?"}, {"role": "assistant", "content": "Chi phí mua của hàng tồn kho gồm giá mua, thuế không được hoàn lại, chi phí vận chuyển, bốc xếp, bảo quản trong quá trình mua hàng và các chi phí liên quan trực tiếp khác."}, {"role": "user", "content": "Còn chi phí nhân công thì có liên quan đến hàng tồn kho không?"}, {"role": "assistant", "content": "Có thể có trong chi phí chế biến hàng tồn kho, ví dụ chi phí nhân công trực tiếp liên quan đến sản phẩm sản xuất."}]</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>VAS về hàng tồn kho có quy định mức lương tối thiểu cho nhân viên không?</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này bị lệch phạm vi của tài liệu VAS về hàng tồn kho. Các đoạn liên quan trong tài liệu chỉ nói về cách xác định giá trị hàng tồn kho, chi phí mua, chi phí chế biến và các khoản chi phí được hoặc không được tính vào giá gốc hàng tồn kho. Tài liệu không quy định mức lương tối thiểu cho nhân viên, nên không có căn cứ để trả lời mức lương tối thiểu từ bộ tài liệu này.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>22</v>
+      </c>
+      <c r="B67" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Vậy chuẩn mực này có quy định mức lương tối thiểu cho nhân viên không?</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Chi phí mua của hàng tồn kho gồm những khoản nào?"}, {"role": "assistant", "content": "Chi phí mua của hàng tồn kho gồm giá mua, thuế không được hoàn lại, chi phí vận chuyển, bốc xếp, bảo quản trong quá trình mua hàng và các chi phí liên quan trực tiếp khác."}, {"role": "user", "content": "Còn chi phí nhân công thì có liên quan đến hàng tồn kho không?"}, {"role": "assistant", "content": "Có thể có trong chi phí chế biến hàng tồn kho, ví dụ chi phí nhân công trực tiếp liên quan đến sản phẩm sản xuất."}]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>VAS về hàng tồn kho có quy định mức lương tối thiểu cho nhân viên không?</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này bị lệch phạm vi của tài liệu VAS về hàng tồn kho. Các đoạn liên quan trong tài liệu chỉ nói về cách xác định giá trị hàng tồn kho, chi phí mua, chi phí chế biến và các khoản chi phí được hoặc không được tính vào giá gốc hàng tồn kho. Tài liệu không quy định mức lương tối thiểu cho nhân viên, nên không có căn cứ để trả lời mức lương tối thiểu từ bộ tài liệu này.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>23</v>
+      </c>
+      <c r="B68" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Vậy doanh nghiệp phải kê khai thuế GTGT hàng tháng theo quy định nào ở đây?</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Doanh thu là gì?"}, {"role": "assistant", "content": "Doanh thu là tổng giá trị các lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán từ hoạt động sản xuất, kinh doanh thông thường và góp phần làm tăng vốn chủ sở hữu."}, {"role": "user", "content": "Khi nào doanh thu bán hàng được ghi nhận?"}, {"role": "assistant", "content": "Doanh thu bán hàng được ghi nhận khi đồng thời thỏa mãn các điều kiện về chuyển giao rủi ro và lợi ích, không còn quyền quản lý hoặc kiểm soát hàng hóa, xác định chắc chắn doanh thu, thu được lợi ích kinh tế và xác định được chi phí liên quan."}]</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>VAS về doanh thu có quy định việc kê khai thuế GTGT hàng tháng không?</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này lệch sang nghĩa vụ kê khai thuế GTGT, trong khi tài liệu VAS đang dùng chỉ quy định về kế toán doanh thu và thu nhập khác, bao gồm định nghĩa doanh thu và điều kiện ghi nhận doanh thu bán hàng. Tài liệu không cung cấp quy định về kê khai thuế GTGT hàng tháng, nên không có căn cứ để trả lời nội dung này từ bộ dữ liệu hiện tại.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>23</v>
+      </c>
+      <c r="B69" t="n">
+        <v>3</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Vậy doanh nghiệp phải kê khai thuế GTGT hàng tháng theo quy định nào ở đây?</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Doanh thu là gì?"}, {"role": "assistant", "content": "Doanh thu là tổng giá trị các lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán từ hoạt động sản xuất, kinh doanh thông thường và góp phần làm tăng vốn chủ sở hữu."}, {"role": "user", "content": "Khi nào doanh thu bán hàng được ghi nhận?"}, {"role": "assistant", "content": "Doanh thu bán hàng được ghi nhận khi đồng thời thỏa mãn các điều kiện về chuyển giao rủi ro và lợi ích, không còn quyền quản lý hoặc kiểm soát hàng hóa, xác định chắc chắn doanh thu, thu được lợi ích kinh tế và xác định được chi phí liên quan."}]</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>VAS về doanh thu có quy định việc kê khai thuế GTGT hàng tháng không?</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này lệch sang nghĩa vụ kê khai thuế GTGT, trong khi tài liệu VAS đang dùng chỉ quy định về kế toán doanh thu và thu nhập khác, bao gồm định nghĩa doanh thu và điều kiện ghi nhận doanh thu bán hàng. Tài liệu không cung cấp quy định về kê khai thuế GTGT hàng tháng, nên không có căn cứ để trả lời nội dung này từ bộ dữ liệu hiện tại.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>23</v>
+      </c>
+      <c r="B70" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Vậy doanh nghiệp phải kê khai thuế GTGT hàng tháng theo quy định nào ở đây?</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Doanh thu là gì?"}, {"role": "assistant", "content": "Doanh thu là tổng giá trị các lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán từ hoạt động sản xuất, kinh doanh thông thường và góp phần làm tăng vốn chủ sở hữu."}, {"role": "user", "content": "Khi nào doanh thu bán hàng được ghi nhận?"}, {"role": "assistant", "content": "Doanh thu bán hàng được ghi nhận khi đồng thời thỏa mãn các điều kiện về chuyển giao rủi ro và lợi ích, không còn quyền quản lý hoặc kiểm soát hàng hóa, xác định chắc chắn doanh thu, thu được lợi ích kinh tế và xác định được chi phí liên quan."}]</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>VAS về doanh thu có quy định việc kê khai thuế GTGT hàng tháng không?</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này lệch sang nghĩa vụ kê khai thuế GTGT, trong khi tài liệu VAS đang dùng chỉ quy định về kế toán doanh thu và thu nhập khác, bao gồm định nghĩa doanh thu và điều kiện ghi nhận doanh thu bán hàng. Tài liệu không cung cấp quy định về kê khai thuế GTGT hàng tháng, nên không có căn cứ để trả lời nội dung này từ bộ dữ liệu hiện tại.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>24</v>
+      </c>
+      <c r="B71" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Vậy phần mềm AI tạo sinh có được coi là tài sản cố định vô hình theo VAS không?</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định vô hình được hiểu là gì?"}, {"role": "assistant", "content": "Tài sản cố định vô hình là tài sản không có hình thái vật chất nhưng xác định được giá trị và do doanh nghiệp nắm giữ, sử dụng trong sản xuất kinh doanh, cung cấp dịch vụ hoặc cho thuê, phù hợp với tiêu chuẩn ghi nhận tài sản cố định vô hình."}, {"role": "user", "content": "Phần mềm máy tính có thể là nguồn lực vô hình không?"}, {"role": "assistant", "content": "Tài liệu có nêu phần mềm máy vi tính là một ví dụ về nguồn lực vô hình mà doanh nghiệp thường đầu tư."}]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Phần mềm AI tạo sinh có được ghi nhận là tài sản cố định vô hình theo kế toán VAS không?</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để kết luận riêng “phần mềm AI tạo sinh” có được ghi nhận là tài sản cố định vô hình hay không. Tài liệu VAS chỉ nêu định nghĩa tài sản cố định vô hình là tài sản không có hình thái vật chất, xác định được giá trị, do doanh nghiệp nắm giữ và sử dụng trong sản xuất, kinh doanh, cung cấp dịch vụ hoặc cho thuê, phù hợp với tiêu chuẩn ghi nhận. Tài liệu không đề cập riêng đến phần mềm AI tạo sinh, nên cần đánh giá theo định nghĩa và tiêu chuẩn ghi nhận, không được tự động kết luận chỉ từ tên loại phần mềm. (Nguồn liên quan: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>24</v>
+      </c>
+      <c r="B72" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Vậy phần mềm AI tạo sinh có được coi là tài sản cố định vô hình theo VAS không?</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định vô hình được hiểu là gì?"}, {"role": "assistant", "content": "Tài sản cố định vô hình là tài sản không có hình thái vật chất nhưng xác định được giá trị và do doanh nghiệp nắm giữ, sử dụng trong sản xuất kinh doanh, cung cấp dịch vụ hoặc cho thuê, phù hợp với tiêu chuẩn ghi nhận tài sản cố định vô hình."}, {"role": "user", "content": "Phần mềm máy tính có thể là nguồn lực vô hình không?"}, {"role": "assistant", "content": "Tài liệu có nêu phần mềm máy vi tính là một ví dụ về nguồn lực vô hình mà doanh nghiệp thường đầu tư."}]</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Phần mềm AI tạo sinh có được ghi nhận là tài sản cố định vô hình theo kế toán VAS không?</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để kết luận riêng “phần mềm AI tạo sinh” có được ghi nhận là tài sản cố định vô hình hay không. Tài liệu VAS chỉ nêu định nghĩa tài sản cố định vô hình là tài sản không có hình thái vật chất, xác định được giá trị, do doanh nghiệp nắm giữ và sử dụng trong sản xuất, kinh doanh, cung cấp dịch vụ hoặc cho thuê, phù hợp với tiêu chuẩn ghi nhận. Tài liệu không đề cập riêng đến phần mềm AI tạo sinh, nên cần đánh giá theo định nghĩa và tiêu chuẩn ghi nhận, không được tự động kết luận chỉ từ tên loại phần mềm. (Nguồn liên quan: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>24</v>
+      </c>
+      <c r="B73" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Vậy phần mềm AI tạo sinh có được coi là tài sản cố định vô hình theo VAS không?</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định vô hình được hiểu là gì?"}, {"role": "assistant", "content": "Tài sản cố định vô hình là tài sản không có hình thái vật chất nhưng xác định được giá trị và do doanh nghiệp nắm giữ, sử dụng trong sản xuất kinh doanh, cung cấp dịch vụ hoặc cho thuê, phù hợp với tiêu chuẩn ghi nhận tài sản cố định vô hình."}, {"role": "user", "content": "Phần mềm máy tính có thể là nguồn lực vô hình không?"}, {"role": "assistant", "content": "Tài liệu có nêu phần mềm máy vi tính là một ví dụ về nguồn lực vô hình mà doanh nghiệp thường đầu tư."}]</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Phần mềm AI tạo sinh có được ghi nhận là tài sản cố định vô hình theo kế toán VAS không?</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để kết luận riêng “phần mềm AI tạo sinh” có được ghi nhận là tài sản cố định vô hình hay không. Tài liệu VAS chỉ nêu định nghĩa tài sản cố định vô hình là tài sản không có hình thái vật chất, xác định được giá trị, do doanh nghiệp nắm giữ và sử dụng trong sản xuất, kinh doanh, cung cấp dịch vụ hoặc cho thuê, phù hợp với tiêu chuẩn ghi nhận. Tài liệu không đề cập riêng đến phần mềm AI tạo sinh, nên cần đánh giá theo định nghĩa và tiêu chuẩn ghi nhận, không được tự động kết luận chỉ từ tên loại phần mềm. (Nguồn liên quan: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ QUY ĐỊNH CHUNG ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>25</v>
+      </c>
+      <c r="B74" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Vậy chuẩn mực này có hướng dẫn cách tính lãi vay ngân hàng năm 2026 không?</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Bất động sản đầu tư là gì?"}, {"role": "assistant", "content": "Bất động sản đầu tư là bất động sản được nắm giữ nhằm mục đích thu lợi từ việc cho thuê hoặc chờ tăng giá, không phải để sử dụng trong sản xuất, cung cấp dịch vụ, quản lý hoặc bán trong kỳ kinh doanh thông thường."}, {"role": "user", "content": "Nguyên giá của bất động sản đầu tư được hiểu thế nào?"}, {"role": "assistant", "content": "Nguyên giá là toàn bộ các chi phí bằng tiền hoặc tương đương tiền mà doanh nghiệp bỏ ra, hoặc giá trị hợp lý của các khoản đưa ra để trao đổi nhằm có được bất động sản đầu tư đến thời điểm mua hoặc xây dựng hoàn thành."}]</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>VAS về bất động sản đầu tư có hướng dẫn cách tính lãi vay ngân hàng năm 2026 không?</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này đi ra ngoài phạm vi nội dung đang có trong tài liệu. Phần VAS về bất động sản đầu tư quy định khái niệm bất động sản đầu tư, nguyên giá, giá trị còn lại, ví dụ và cách xử lý một số trường hợp kế toán liên quan đến bất động sản đầu tư. Tài liệu không hướng dẫn cách tính lãi vay ngân hàng năm 2026, nên không có căn cứ để trả lời nội dung đó từ bộ dữ liệu hiện tại.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>25</v>
+      </c>
+      <c r="B75" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Vậy chuẩn mực này có hướng dẫn cách tính lãi vay ngân hàng năm 2026 không?</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Bất động sản đầu tư là gì?"}, {"role": "assistant", "content": "Bất động sản đầu tư là bất động sản được nắm giữ nhằm mục đích thu lợi từ việc cho thuê hoặc chờ tăng giá, không phải để sử dụng trong sản xuất, cung cấp dịch vụ, quản lý hoặc bán trong kỳ kinh doanh thông thường."}, {"role": "user", "content": "Nguyên giá của bất động sản đầu tư được hiểu thế nào?"}, {"role": "assistant", "content": "Nguyên giá là toàn bộ các chi phí bằng tiền hoặc tương đương tiền mà doanh nghiệp bỏ ra, hoặc giá trị hợp lý của các khoản đưa ra để trao đổi nhằm có được bất động sản đầu tư đến thời điểm mua hoặc xây dựng hoàn thành."}]</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>VAS về bất động sản đầu tư có hướng dẫn cách tính lãi vay ngân hàng năm 2026 không?</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này đi ra ngoài phạm vi nội dung đang có trong tài liệu. Phần VAS về bất động sản đầu tư quy định khái niệm bất động sản đầu tư, nguyên giá, giá trị còn lại, ví dụ và cách xử lý một số trường hợp kế toán liên quan đến bất động sản đầu tư. Tài liệu không hướng dẫn cách tính lãi vay ngân hàng năm 2026, nên không có căn cứ để trả lời nội dung đó từ bộ dữ liệu hiện tại.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>25</v>
+      </c>
+      <c r="B76" t="n">
+        <v>3</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Vậy chuẩn mực này có hướng dẫn cách tính lãi vay ngân hàng năm 2026 không?</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Bất động sản đầu tư là gì?"}, {"role": "assistant", "content": "Bất động sản đầu tư là bất động sản được nắm giữ nhằm mục đích thu lợi từ việc cho thuê hoặc chờ tăng giá, không phải để sử dụng trong sản xuất, cung cấp dịch vụ, quản lý hoặc bán trong kỳ kinh doanh thông thường."}, {"role": "user", "content": "Nguyên giá của bất động sản đầu tư được hiểu thế nào?"}, {"role": "assistant", "content": "Nguyên giá là toàn bộ các chi phí bằng tiền hoặc tương đương tiền mà doanh nghiệp bỏ ra, hoặc giá trị hợp lý của các khoản đưa ra để trao đổi nhằm có được bất động sản đầu tư đến thời điểm mua hoặc xây dựng hoàn thành."}]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>VAS về bất động sản đầu tư có hướng dẫn cách tính lãi vay ngân hàng năm 2026 không?</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này đi ra ngoài phạm vi nội dung đang có trong tài liệu. Phần VAS về bất động sản đầu tư quy định khái niệm bất động sản đầu tư, nguyên giá, giá trị còn lại, ví dụ và cách xử lý một số trường hợp kế toán liên quan đến bất động sản đầu tư. Tài liệu không hướng dẫn cách tính lãi vay ngân hàng năm 2026, nên không có căn cứ để trả lời nội dung đó từ bộ dữ liệu hiện tại.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>26</v>
+      </c>
+      <c r="B77" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Vậy hợp đồng thuê nhà trên blockchain có được phân loại theo chuẩn mực này không?</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Thuê tài sản là gì?"}, {"role": "assistant", "content": "Thuê tài sản là thỏa thuận giữa bên cho thuê và bên thuê về việc bên cho thuê chuyển quyền sử dụng tài sản cho bên thuê trong một khoảng thời gian nhất định để nhận tiền cho thuê."}, {"role": "user", "content": "Việc phân loại thuê tài sản dựa vào yếu tố nào?"}, {"role": "assistant", "content": "Việc phân loại thuê tài sản căn cứ vào mức độ chuyển giao rủi ro và lợi ích gắn liền với quyền sở hữu tài sản thuê từ bên cho thuê sang bên thuê."}]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Hợp đồng thuê nhà trên blockchain có được phân loại là thuê tài chính hoặc thuê hoạt động theo kế toán VAS không?</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để kết luận riêng về “hợp đồng thuê nhà trên blockchain” từ tài liệu hiện có. VAS về thuê tài sản chỉ nêu nguyên tắc phân loại thuê tài sản dựa vào mức độ chuyển giao rủi ro và lợi ích gắn liền với quyền sở hữu tài sản thuê từ bên cho thuê cho bên thuê. Tài liệu không đề cập blockchain, nên không nên tự suy diễn phân loại chỉ dựa trên hình thức công nghệ của hợp đồng; cần xem bản chất chuyển giao rủi ro và lợi ích theo chuẩn mực. (Nguồn liên quan: CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>26</v>
+      </c>
+      <c r="B78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Vậy hợp đồng thuê nhà trên blockchain có được phân loại theo chuẩn mực này không?</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Thuê tài sản là gì?"}, {"role": "assistant", "content": "Thuê tài sản là thỏa thuận giữa bên cho thuê và bên thuê về việc bên cho thuê chuyển quyền sử dụng tài sản cho bên thuê trong một khoảng thời gian nhất định để nhận tiền cho thuê."}, {"role": "user", "content": "Việc phân loại thuê tài sản dựa vào yếu tố nào?"}, {"role": "assistant", "content": "Việc phân loại thuê tài sản căn cứ vào mức độ chuyển giao rủi ro và lợi ích gắn liền với quyền sở hữu tài sản thuê từ bên cho thuê sang bên thuê."}]</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Hợp đồng thuê nhà trên blockchain có được phân loại là thuê tài chính hoặc thuê hoạt động theo kế toán VAS không?</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để kết luận riêng về “hợp đồng thuê nhà trên blockchain” từ tài liệu hiện có. VAS về thuê tài sản chỉ nêu nguyên tắc phân loại thuê tài sản dựa vào mức độ chuyển giao rủi ro và lợi ích gắn liền với quyền sở hữu tài sản thuê từ bên cho thuê cho bên thuê. Tài liệu không đề cập blockchain, nên không nên tự suy diễn phân loại chỉ dựa trên hình thức công nghệ của hợp đồng; cần xem bản chất chuyển giao rủi ro và lợi ích theo chuẩn mực. (Nguồn liên quan: CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>26</v>
+      </c>
+      <c r="B79" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Vậy hợp đồng thuê nhà trên blockchain có được phân loại theo chuẩn mực này không?</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Thuê tài sản là gì?"}, {"role": "assistant", "content": "Thuê tài sản là thỏa thuận giữa bên cho thuê và bên thuê về việc bên cho thuê chuyển quyền sử dụng tài sản cho bên thuê trong một khoảng thời gian nhất định để nhận tiền cho thuê."}, {"role": "user", "content": "Việc phân loại thuê tài sản dựa vào yếu tố nào?"}, {"role": "assistant", "content": "Việc phân loại thuê tài sản căn cứ vào mức độ chuyển giao rủi ro và lợi ích gắn liền với quyền sở hữu tài sản thuê từ bên cho thuê sang bên thuê."}]</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Hợp đồng thuê nhà trên blockchain có được phân loại là thuê tài chính hoặc thuê hoạt động theo kế toán VAS không?</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 06.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để kết luận riêng về “hợp đồng thuê nhà trên blockchain” từ tài liệu hiện có. VAS về thuê tài sản chỉ nêu nguyên tắc phân loại thuê tài sản dựa vào mức độ chuyển giao rủi ro và lợi ích gắn liền với quyền sở hữu tài sản thuê từ bên cho thuê cho bên thuê. Tài liệu không đề cập blockchain, nên không nên tự suy diễn phân loại chỉ dựa trên hình thức công nghệ của hợp đồng; cần xem bản chất chuyển giao rủi ro và lợi ích theo chuẩn mực. (Nguồn liên quan: CHUẨN MỰC SỐ 06 - THUÊ TÀI SẢN ➔ NỘI DUNG CHUẨN MỰC ➔ Phân loại thuê tài sản ➔ 06.)</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>27</v>
+      </c>
+      <c r="B80" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Vậy công ty phải đóng bảo hiểm xã hội bao nhiêu phần trăm cho nhân viên?</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Chi phí nhân công có thể liên quan đến hàng tồn kho không?"}, {"role": "assistant", "content": "Có. Trong chi phí chế biến hàng tồn kho, chi phí nhân công trực tiếp là một khoản chi phí liên quan trực tiếp đến sản phẩm sản xuất."}, {"role": "user", "content": "Vậy các khoản liên quan đến nhân viên có thể ảnh hưởng đến chi phí kế toán đúng không?"}, {"role": "assistant", "content": "Có thể ảnh hưởng đến chi phí kế toán nếu khoản đó thuộc phạm vi chi phí được chuẩn mực đề cập và có căn cứ ghi nhận phù hợp."}]</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>VAS có quy định tỷ lệ đóng bảo hiểm xã hội cho nhân viên không?</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này thuộc domain chính sách lao động/bảo hiểm xã hội, không thuộc phạm vi các đoạn VAS trong tài liệu hiện có. Tài liệu có thể nhắc đến chi phí nhân công trong bối cảnh chi phí kế toán, nhưng không quy định tỷ lệ đóng bảo hiểm xã hội cho nhân viên. Vì vậy không có căn cứ để trả lời tỷ lệ BHXH từ bộ dữ liệu VAS này.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>27</v>
+      </c>
+      <c r="B81" t="n">
+        <v>3</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Vậy công ty phải đóng bảo hiểm xã hội bao nhiêu phần trăm cho nhân viên?</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Chi phí nhân công có thể liên quan đến hàng tồn kho không?"}, {"role": "assistant", "content": "Có. Trong chi phí chế biến hàng tồn kho, chi phí nhân công trực tiếp là một khoản chi phí liên quan trực tiếp đến sản phẩm sản xuất."}, {"role": "user", "content": "Vậy các khoản liên quan đến nhân viên có thể ảnh hưởng đến chi phí kế toán đúng không?"}, {"role": "assistant", "content": "Có thể ảnh hưởng đến chi phí kế toán nếu khoản đó thuộc phạm vi chi phí được chuẩn mực đề cập và có căn cứ ghi nhận phù hợp."}]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>VAS có quy định tỷ lệ đóng bảo hiểm xã hội cho nhân viên không?</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này thuộc domain chính sách lao động/bảo hiểm xã hội, không thuộc phạm vi các đoạn VAS trong tài liệu hiện có. Tài liệu có thể nhắc đến chi phí nhân công trong bối cảnh chi phí kế toán, nhưng không quy định tỷ lệ đóng bảo hiểm xã hội cho nhân viên. Vì vậy không có căn cứ để trả lời tỷ lệ BHXH từ bộ dữ liệu VAS này.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>27</v>
+      </c>
+      <c r="B82" t="n">
+        <v>3</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Vậy công ty phải đóng bảo hiểm xã hội bao nhiêu phần trăm cho nhân viên?</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Chi phí nhân công có thể liên quan đến hàng tồn kho không?"}, {"role": "assistant", "content": "Có. Trong chi phí chế biến hàng tồn kho, chi phí nhân công trực tiếp là một khoản chi phí liên quan trực tiếp đến sản phẩm sản xuất."}, {"role": "user", "content": "Vậy các khoản liên quan đến nhân viên có thể ảnh hưởng đến chi phí kế toán đúng không?"}, {"role": "assistant", "content": "Có thể ảnh hưởng đến chi phí kế toán nếu khoản đó thuộc phạm vi chi phí được chuẩn mực đề cập và có căn cứ ghi nhận phù hợp."}]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>VAS có quy định tỷ lệ đóng bảo hiểm xã hội cho nhân viên không?</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này thuộc domain chính sách lao động/bảo hiểm xã hội, không thuộc phạm vi các đoạn VAS trong tài liệu hiện có. Tài liệu có thể nhắc đến chi phí nhân công trong bối cảnh chi phí kế toán, nhưng không quy định tỷ lệ đóng bảo hiểm xã hội cho nhân viên. Vì vậy không có căn cứ để trả lời tỷ lệ BHXH từ bộ dữ liệu VAS này.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>28</v>
+      </c>
+      <c r="B83" t="n">
+        <v>3</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Nếu làm theo IFRS thì khoản này có xử lý giống vậy không?</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định vô hình có giá trị thanh lý khi nào?"}, {"role": "assistant", "content": "Tài sản cố định vô hình có giá trị thanh lý khi có bên thứ ba thỏa thuận mua lại tài sản vào cuối thời gian sử dụng hữu ích, hoặc có thị trường hoạt động ở cuối thời gian sử dụng hữu ích và giá trị thanh lý xác định được qua giá thị trường."}, {"role": "user", "content": "Nếu không có các điều kiện đó thì sao?"}, {"role": "assistant", "content": "Nếu không có một trong hai điều kiện đó thì giá trị thanh lý của tài sản cố định vô hình được xác định bằng không."}]</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>IFRS có xử lý giá trị thanh lý của tài sản cố định vô hình giống VAS không?</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để so sánh với IFRS từ tài liệu hiện có. Bộ dữ liệu đang dùng là nội dung VAS, chỉ nêu cách xác định giá trị thanh lý của tài sản cố định vô hình theo VAS. Tài liệu không chứa quy định IFRS, nên không thể kết luận IFRS xử lý giống hay khác VAS nếu không bổ sung nguồn IFRS tương ứng.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>28</v>
+      </c>
+      <c r="B84" t="n">
+        <v>3</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Nếu làm theo IFRS thì khoản này có xử lý giống vậy không?</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định vô hình có giá trị thanh lý khi nào?"}, {"role": "assistant", "content": "Tài sản cố định vô hình có giá trị thanh lý khi có bên thứ ba thỏa thuận mua lại tài sản vào cuối thời gian sử dụng hữu ích, hoặc có thị trường hoạt động ở cuối thời gian sử dụng hữu ích và giá trị thanh lý xác định được qua giá thị trường."}, {"role": "user", "content": "Nếu không có các điều kiện đó thì sao?"}, {"role": "assistant", "content": "Nếu không có một trong hai điều kiện đó thì giá trị thanh lý của tài sản cố định vô hình được xác định bằng không."}]</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>IFRS có xử lý giá trị thanh lý của tài sản cố định vô hình giống VAS không?</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để so sánh với IFRS từ tài liệu hiện có. Bộ dữ liệu đang dùng là nội dung VAS, chỉ nêu cách xác định giá trị thanh lý của tài sản cố định vô hình theo VAS. Tài liệu không chứa quy định IFRS, nên không thể kết luận IFRS xử lý giống hay khác VAS nếu không bổ sung nguồn IFRS tương ứng.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>28</v>
+      </c>
+      <c r="B85" t="n">
+        <v>3</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Nếu làm theo IFRS thì khoản này có xử lý giống vậy không?</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định vô hình có giá trị thanh lý khi nào?"}, {"role": "assistant", "content": "Tài sản cố định vô hình có giá trị thanh lý khi có bên thứ ba thỏa thuận mua lại tài sản vào cuối thời gian sử dụng hữu ích, hoặc có thị trường hoạt động ở cuối thời gian sử dụng hữu ích và giá trị thanh lý xác định được qua giá thị trường."}, {"role": "user", "content": "Nếu không có các điều kiện đó thì sao?"}, {"role": "assistant", "content": "Nếu không có một trong hai điều kiện đó thì giá trị thanh lý của tài sản cố định vô hình được xác định bằng không."}]</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>IFRS có xử lý giá trị thanh lý của tài sản cố định vô hình giống VAS không?</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để so sánh với IFRS từ tài liệu hiện có. Bộ dữ liệu đang dùng là nội dung VAS, chỉ nêu cách xác định giá trị thanh lý của tài sản cố định vô hình theo VAS. Tài liệu không chứa quy định IFRS, nên không thể kết luận IFRS xử lý giống hay khác VAS nếu không bổ sung nguồn IFRS tương ứng.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>29</v>
+      </c>
+      <c r="B86" t="n">
+        <v>3</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Vậy doanh nghiệp có cần xin giấy phép xây dựng trước khi ghi nhận hợp đồng không?</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hợp đồng xây dựng là gì?"}, {"role": "assistant", "content": "Hợp đồng xây dựng là hợp đồng bằng văn bản về việc xây dựng một tài sản hoặc một tổ hợp tài sản có liên quan chặt chẽ hoặc phụ thuộc lẫn nhau về thiết kế, công nghệ, chức năng hoặc mục đích sử dụng cơ bản."}, {"role": "user", "content": "Doanh thu của hợp đồng xây dựng gồm những khoản nào?"}, {"role": "assistant", "content": "Doanh thu của hợp đồng xây dựng gồm doanh thu ban đầu trong hợp đồng và các khoản tăng, giảm, tiền thưởng, các khoản thanh toán khác nếu có khả năng làm thay đổi doanh thu và xác định được đáng tin cậy."}]</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>VAS về hợp đồng xây dựng có quy định thủ tục xin giấy phép xây dựng không?</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này thuộc domain thủ tục pháp lý/xây dựng, không thuộc phạm vi quy định kế toán trong tài liệu VAS hiện có. Chuẩn mực về hợp đồng xây dựng trong bộ dữ liệu đề cập khái niệm hợp đồng xây dựng, doanh thu và chi phí hợp đồng xây dựng, không hướng dẫn thủ tục xin giấy phép xây dựng. Vì vậy không có căn cứ để trả lời nội dung này từ tài liệu VAS.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>29</v>
+      </c>
+      <c r="B87" t="n">
+        <v>3</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Vậy doanh nghiệp có cần xin giấy phép xây dựng trước khi ghi nhận hợp đồng không?</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hợp đồng xây dựng là gì?"}, {"role": "assistant", "content": "Hợp đồng xây dựng là hợp đồng bằng văn bản về việc xây dựng một tài sản hoặc một tổ hợp tài sản có liên quan chặt chẽ hoặc phụ thuộc lẫn nhau về thiết kế, công nghệ, chức năng hoặc mục đích sử dụng cơ bản."}, {"role": "user", "content": "Doanh thu của hợp đồng xây dựng gồm những khoản nào?"}, {"role": "assistant", "content": "Doanh thu của hợp đồng xây dựng gồm doanh thu ban đầu trong hợp đồng và các khoản tăng, giảm, tiền thưởng, các khoản thanh toán khác nếu có khả năng làm thay đổi doanh thu và xác định được đáng tin cậy."}]</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>VAS về hợp đồng xây dựng có quy định thủ tục xin giấy phép xây dựng không?</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này thuộc domain thủ tục pháp lý/xây dựng, không thuộc phạm vi quy định kế toán trong tài liệu VAS hiện có. Chuẩn mực về hợp đồng xây dựng trong bộ dữ liệu đề cập khái niệm hợp đồng xây dựng, doanh thu và chi phí hợp đồng xây dựng, không hướng dẫn thủ tục xin giấy phép xây dựng. Vì vậy không có căn cứ để trả lời nội dung này từ tài liệu VAS.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>29</v>
+      </c>
+      <c r="B88" t="n">
+        <v>3</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Vậy doanh nghiệp có cần xin giấy phép xây dựng trước khi ghi nhận hợp đồng không?</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hợp đồng xây dựng là gì?"}, {"role": "assistant", "content": "Hợp đồng xây dựng là hợp đồng bằng văn bản về việc xây dựng một tài sản hoặc một tổ hợp tài sản có liên quan chặt chẽ hoặc phụ thuộc lẫn nhau về thiết kế, công nghệ, chức năng hoặc mục đích sử dụng cơ bản."}, {"role": "user", "content": "Doanh thu của hợp đồng xây dựng gồm những khoản nào?"}, {"role": "assistant", "content": "Doanh thu của hợp đồng xây dựng gồm doanh thu ban đầu trong hợp đồng và các khoản tăng, giảm, tiền thưởng, các khoản thanh toán khác nếu có khả năng làm thay đổi doanh thu và xác định được đáng tin cậy."}]</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>VAS về hợp đồng xây dựng có quy định thủ tục xin giấy phép xây dựng không?</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Không. Câu hỏi này thuộc domain thủ tục pháp lý/xây dựng, không thuộc phạm vi quy định kế toán trong tài liệu VAS hiện có. Chuẩn mực về hợp đồng xây dựng trong bộ dữ liệu đề cập khái niệm hợp đồng xây dựng, doanh thu và chi phí hợp đồng xây dựng, không hướng dẫn thủ tục xin giấy phép xây dựng. Vì vậy không có căn cứ để trả lời nội dung này từ tài liệu VAS.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>30</v>
+      </c>
+      <c r="B89" t="n">
+        <v>3</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Nếu khách hàng thanh toán bằng NFT thì doanh thu được ghi nhận thế nào?</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Doanh thu là gì?"}, {"role": "assistant", "content": "Doanh thu là tổng giá trị các lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán từ hoạt động sản xuất, kinh doanh thông thường và góp phần làm tăng vốn chủ sở hữu."}, {"role": "user", "content": "Khi nào doanh thu bán hàng được ghi nhận?"}, {"role": "assistant", "content": "Doanh thu bán hàng được ghi nhận khi thỏa mãn đồng thời các điều kiện về chuyển giao rủi ro và lợi ích, không còn kiểm soát hàng hóa, xác định chắc chắn doanh thu, thu được lợi ích kinh tế và xác định được chi phí liên quan."}]</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>VAS có hướng dẫn ghi nhận doanh thu khi khách hàng thanh toán bằng NFT không?</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để trả lời riêng trường hợp khách hàng thanh toán bằng NFT từ tài liệu hiện có. VAS về doanh thu bán hàng chỉ nêu các điều kiện ghi nhận doanh thu bán hàng như chuyển giao phần lớn rủi ro và lợi ích, không còn quyền quản lý/kiểm soát hàng hóa, doanh thu xác định tương đối chắc chắn, thu được hoặc sẽ thu được lợi ích kinh tế và xác định được chi phí liên quan. Tài liệu không đề cập NFT, nên không nên suy diễn cách ghi nhận doanh thu cho hình thức thanh toán này nếu không có nguồn bổ sung. (Nguồn liên quan: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.)</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>30</v>
+      </c>
+      <c r="B90" t="n">
+        <v>3</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Nếu khách hàng thanh toán bằng NFT thì doanh thu được ghi nhận thế nào?</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Doanh thu là gì?"}, {"role": "assistant", "content": "Doanh thu là tổng giá trị các lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán từ hoạt động sản xuất, kinh doanh thông thường và góp phần làm tăng vốn chủ sở hữu."}, {"role": "user", "content": "Khi nào doanh thu bán hàng được ghi nhận?"}, {"role": "assistant", "content": "Doanh thu bán hàng được ghi nhận khi thỏa mãn đồng thời các điều kiện về chuyển giao rủi ro và lợi ích, không còn kiểm soát hàng hóa, xác định chắc chắn doanh thu, thu được lợi ích kinh tế và xác định được chi phí liên quan."}]</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>VAS có hướng dẫn ghi nhận doanh thu khi khách hàng thanh toán bằng NFT không?</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để trả lời riêng trường hợp khách hàng thanh toán bằng NFT từ tài liệu hiện có. VAS về doanh thu bán hàng chỉ nêu các điều kiện ghi nhận doanh thu bán hàng như chuyển giao phần lớn rủi ro và lợi ích, không còn quyền quản lý/kiểm soát hàng hóa, doanh thu xác định tương đối chắc chắn, thu được hoặc sẽ thu được lợi ích kinh tế và xác định được chi phí liên quan. Tài liệu không đề cập NFT, nên không nên suy diễn cách ghi nhận doanh thu cho hình thức thanh toán này nếu không có nguồn bổ sung. (Nguồn liên quan: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.)</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>30</v>
+      </c>
+      <c r="B91" t="n">
+        <v>3</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Nếu khách hàng thanh toán bằng NFT thì doanh thu được ghi nhận thế nào?</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Doanh thu là gì?"}, {"role": "assistant", "content": "Doanh thu là tổng giá trị các lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán từ hoạt động sản xuất, kinh doanh thông thường và góp phần làm tăng vốn chủ sở hữu."}, {"role": "user", "content": "Khi nào doanh thu bán hàng được ghi nhận?"}, {"role": "assistant", "content": "Doanh thu bán hàng được ghi nhận khi thỏa mãn đồng thời các điều kiện về chuyển giao rủi ro và lợi ích, không còn kiểm soát hàng hóa, xác định chắc chắn doanh thu, thu được lợi ích kinh tế và xác định được chi phí liên quan."}]</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>VAS có hướng dẫn ghi nhận doanh thu khi khách hàng thanh toán bằng NFT không?</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Không đủ căn cứ để trả lời riêng trường hợp khách hàng thanh toán bằng NFT từ tài liệu hiện có. VAS về doanh thu bán hàng chỉ nêu các điều kiện ghi nhận doanh thu bán hàng như chuyển giao phần lớn rủi ro và lợi ích, không còn quyền quản lý/kiểm soát hàng hóa, doanh thu xác định tương đối chắc chắn, thu được hoặc sẽ thu được lợi ích kinh tế và xác định được chi phí liên quan. Tài liệu không đề cập NFT, nên không nên suy diễn cách ghi nhận doanh thu cho hình thức thanh toán này nếu không có nguồn bổ sung. (Nguồn liên quan: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.)</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>31</v>
+      </c>
+      <c r="B92" t="n">
+        <v>4</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Một bất động sản vừa được dùng cho hoạt động của doanh nghiệp vừa có phần cho thuê thì có được coi là bất động sản đầu tư không, và khi nào phải chuyển mục đích sử dụng của nó?</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Bất động sản đầu tư là gì?"}, {"role": "assistant", "content": "Bất động sản đầu tư là bất động sản được nắm giữ nhằm thu lợi từ việc cho thuê hoặc chờ tăng giá, không phải để sử dụng trong sản xuất, cung cấp dịch vụ, quản lý hoặc bán trong kỳ kinh doanh thông thường."}, {"role": "user", "content": "Nếu cùng một bất động sản có nhiều mục đích sử dụng thì sao?"}, {"role": "assistant", "content": "Khi đó cần xem từng phần tài sản có thể hạch toán riêng hay không, và phải phân biệt với trường hợp chuyển đổi mục đích sử dụng."}]</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Bất động sản dùng hỗn hợp được hạch toán thế nào và khi nào được chuyển mục đích sử dụng trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ QUY ĐỊNH CHUNG ➔ 08.
+CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ NỘI DUNG CHUẨN MỰC ➔ Chuyển đổi mục đích sử dụng ➔ 23.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Nếu một bất động sản được doanh nghiệp nắm giữ một phần để cho thuê hoạt động hoặc chờ tăng giá, và một phần dùng cho sản xuất, cung cấp hàng hóa, dịch vụ hoặc quản lý, thì phải xét khả năng tách riêng các phần tài sản. Nếu các phần này có thể bán riêng rẽ hoặc cho thuê riêng rẽ, doanh nghiệp hạch toán từng phần một cách riêng rẽ. Nếu không thể bán riêng rẽ, bất động sản chỉ được coi là bất động sản đầu tư khi phần dùng cho sản xuất, cung cấp hàng hóa, dịch vụ hoặc quản lý là không đáng kể. (Nguồn: CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ QUY ĐỊNH CHUNG ➔ 08.)
+Ý từ nguồn 2: Việc chuyển đổi giữa bất động sản đầu tư, bất động sản chủ sở hữu sử dụng và hàng tồn kho chỉ thực hiện khi có thay đổi mục đích sử dụng. Ví dụ, bất động sản đầu tư chuyển thành bất động sản chủ sở hữu sử dụng khi chủ sở hữu bắt đầu sử dụng tài sản; chuyển thành hàng tồn kho khi bắt đầu triển khai để bán; bất động sản chủ sở hữu sử dụng chuyển thành bất động sản đầu tư khi chủ sở hữu kết thúc sử dụng; hàng tồn kho chuyển thành bất động sản đầu tư khi bắt đầu cho thuê hoạt động. (Nguồn: CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ NỘI DUNG CHUẨN MỰC ➔ Chuyển đổi mục đích sử dụng ➔ 23.)
+Trả lời câu hỏi: Với bất động sản dùng hỗn hợp, trước hết doanh nghiệp phải xác định có thể tách phần cho thuê/chờ tăng giá và phần dùng cho hoạt động của doanh nghiệp hay không. Nếu tách được thì hạch toán riêng; nếu không tách được thì chỉ coi là bất động sản đầu tư khi phần dùng cho hoạt động doanh nghiệp là không đáng kể. Việc chuyển mục đích sử dụng không dựa vào ý định chung chung mà chỉ thực hiện khi có sự thay đổi mục đích sử dụng thực tế theo các trường hợp nêu trong chuẩn mực.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>31</v>
+      </c>
+      <c r="B93" t="n">
+        <v>4</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Một bất động sản vừa được dùng cho hoạt động của doanh nghiệp vừa có phần cho thuê thì có được coi là bất động sản đầu tư không, và khi nào phải chuyển mục đích sử dụng của nó?</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Bất động sản đầu tư là gì?"}, {"role": "assistant", "content": "Bất động sản đầu tư là bất động sản được nắm giữ nhằm thu lợi từ việc cho thuê hoặc chờ tăng giá, không phải để sử dụng trong sản xuất, cung cấp dịch vụ, quản lý hoặc bán trong kỳ kinh doanh thông thường."}, {"role": "user", "content": "Nếu cùng một bất động sản có nhiều mục đích sử dụng thì sao?"}, {"role": "assistant", "content": "Khi đó cần xem từng phần tài sản có thể hạch toán riêng hay không, và phải phân biệt với trường hợp chuyển đổi mục đích sử dụng."}]</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Bất động sản dùng hỗn hợp được hạch toán thế nào và khi nào được chuyển mục đích sử dụng trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ QUY ĐỊNH CHUNG ➔ 08.
+CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ NỘI DUNG CHUẨN MỰC ➔ Chuyển đổi mục đích sử dụng ➔ 23.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Nếu một bất động sản được doanh nghiệp nắm giữ một phần để cho thuê hoạt động hoặc chờ tăng giá, và một phần dùng cho sản xuất, cung cấp hàng hóa, dịch vụ hoặc quản lý, thì phải xét khả năng tách riêng các phần tài sản. Nếu các phần này có thể bán riêng rẽ hoặc cho thuê riêng rẽ, doanh nghiệp hạch toán từng phần một cách riêng rẽ. Nếu không thể bán riêng rẽ, bất động sản chỉ được coi là bất động sản đầu tư khi phần dùng cho sản xuất, cung cấp hàng hóa, dịch vụ hoặc quản lý là không đáng kể. (Nguồn: CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ QUY ĐỊNH CHUNG ➔ 08.)
+Ý từ nguồn 2: Việc chuyển đổi giữa bất động sản đầu tư, bất động sản chủ sở hữu sử dụng và hàng tồn kho chỉ thực hiện khi có thay đổi mục đích sử dụng. Ví dụ, bất động sản đầu tư chuyển thành bất động sản chủ sở hữu sử dụng khi chủ sở hữu bắt đầu sử dụng tài sản; chuyển thành hàng tồn kho khi bắt đầu triển khai để bán; bất động sản chủ sở hữu sử dụng chuyển thành bất động sản đầu tư khi chủ sở hữu kết thúc sử dụng; hàng tồn kho chuyển thành bất động sản đầu tư khi bắt đầu cho thuê hoạt động. (Nguồn: CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ NỘI DUNG CHUẨN MỰC ➔ Chuyển đổi mục đích sử dụng ➔ 23.)
+Trả lời câu hỏi: Với bất động sản dùng hỗn hợp, trước hết doanh nghiệp phải xác định có thể tách phần cho thuê/chờ tăng giá và phần dùng cho hoạt động của doanh nghiệp hay không. Nếu tách được thì hạch toán riêng; nếu không tách được thì chỉ coi là bất động sản đầu tư khi phần dùng cho hoạt động doanh nghiệp là không đáng kể. Việc chuyển mục đích sử dụng không dựa vào ý định chung chung mà chỉ thực hiện khi có sự thay đổi mục đích sử dụng thực tế theo các trường hợp nêu trong chuẩn mực.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>31</v>
+      </c>
+      <c r="B94" t="n">
+        <v>4</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Một bất động sản vừa được dùng cho hoạt động của doanh nghiệp vừa có phần cho thuê thì có được coi là bất động sản đầu tư không, và khi nào phải chuyển mục đích sử dụng của nó?</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Bất động sản đầu tư là gì?"}, {"role": "assistant", "content": "Bất động sản đầu tư là bất động sản được nắm giữ nhằm thu lợi từ việc cho thuê hoặc chờ tăng giá, không phải để sử dụng trong sản xuất, cung cấp dịch vụ, quản lý hoặc bán trong kỳ kinh doanh thông thường."}, {"role": "user", "content": "Nếu cùng một bất động sản có nhiều mục đích sử dụng thì sao?"}, {"role": "assistant", "content": "Khi đó cần xem từng phần tài sản có thể hạch toán riêng hay không, và phải phân biệt với trường hợp chuyển đổi mục đích sử dụng."}]</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Bất động sản dùng hỗn hợp được hạch toán thế nào và khi nào được chuyển mục đích sử dụng trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ QUY ĐỊNH CHUNG ➔ 08.
+CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ NỘI DUNG CHUẨN MỰC ➔ Chuyển đổi mục đích sử dụng ➔ 23.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Nếu một bất động sản được doanh nghiệp nắm giữ một phần để cho thuê hoạt động hoặc chờ tăng giá, và một phần dùng cho sản xuất, cung cấp hàng hóa, dịch vụ hoặc quản lý, thì phải xét khả năng tách riêng các phần tài sản. Nếu các phần này có thể bán riêng rẽ hoặc cho thuê riêng rẽ, doanh nghiệp hạch toán từng phần một cách riêng rẽ. Nếu không thể bán riêng rẽ, bất động sản chỉ được coi là bất động sản đầu tư khi phần dùng cho sản xuất, cung cấp hàng hóa, dịch vụ hoặc quản lý là không đáng kể. (Nguồn: CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ QUY ĐỊNH CHUNG ➔ 08.)
+Ý từ nguồn 2: Việc chuyển đổi giữa bất động sản đầu tư, bất động sản chủ sở hữu sử dụng và hàng tồn kho chỉ thực hiện khi có thay đổi mục đích sử dụng. Ví dụ, bất động sản đầu tư chuyển thành bất động sản chủ sở hữu sử dụng khi chủ sở hữu bắt đầu sử dụng tài sản; chuyển thành hàng tồn kho khi bắt đầu triển khai để bán; bất động sản chủ sở hữu sử dụng chuyển thành bất động sản đầu tư khi chủ sở hữu kết thúc sử dụng; hàng tồn kho chuyển thành bất động sản đầu tư khi bắt đầu cho thuê hoạt động. (Nguồn: CHUẨN MỰC SỐ 05 - BẤT ĐỘNG SẢN ĐẦU TƯ ➔ NỘI DUNG CHUẨN MỰC ➔ Chuyển đổi mục đích sử dụng ➔ 23.)
+Trả lời câu hỏi: Với bất động sản dùng hỗn hợp, trước hết doanh nghiệp phải xác định có thể tách phần cho thuê/chờ tăng giá và phần dùng cho hoạt động của doanh nghiệp hay không. Nếu tách được thì hạch toán riêng; nếu không tách được thì chỉ coi là bất động sản đầu tư khi phần dùng cho hoạt động doanh nghiệp là không đáng kể. Việc chuyển mục đích sử dụng không dựa vào ý định chung chung mà chỉ thực hiện khi có sự thay đổi mục đích sử dụng thực tế theo các trường hợp nêu trong chuẩn mực.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>32</v>
+      </c>
+      <c r="B95" t="n">
+        <v>4</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Khi đánh giá hàng tồn kho, doanh nghiệp vừa phải chọn phương pháp tính giá trị vừa phải xem xét việc ghi giảm giá gốc trong trường hợp nào?</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hàng tồn kho được tính theo giá nào?"}, {"role": "assistant", "content": "Hàng tồn kho được tính theo giá gốc; nếu giá trị thuần có thể thực hiện được thấp hơn giá gốc thì phải tính theo giá trị thuần có thể thực hiện được."}]</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Khi đánh giá hàng tồn kho, doanh nghiệp áp dụng các phương pháp tính giá trị nào và khi nào phải ghi giảm giá gốc hàng tồn kho?</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 13.
+CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ TRỊ THUẦN CÓ THỂ THỰC HIỆN ĐƯỢC VÀ LẬP DỰ PHÒNG GIẢM GIÁ HÀNG TỒN KHO ➔ 18.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Về phương pháp tính giá trị, hàng tồn kho được tính theo một trong các phương pháp: giá đích danh, bình quân gia quyền, nhập trước xuất trước, hoặc nhập sau xuất trước. Đây là nhóm quy định về cách xác định giá trị hàng tồn kho để ghi nhận và trình bày. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 13.)
+Ý từ nguồn 2: Riêng việc ghi giảm giá gốc phát sinh khi giá trị hàng tồn kho không thu hồi đủ, chẳng hạn hàng tồn kho bị hư hỏng, lỗi thời, giá bán bị giảm, hoặc chi phí hoàn thiện, chi phí để bán hàng tăng lên. Khi đó, ghi giảm giá gốc xuống bằng giá trị thuần có thể thực hiện được là phù hợp với nguyên tắc tài sản không được phản ánh lớn hơn giá trị thực hiện ước tính từ việc bán hay sử dụng. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ TRỊ THUẦN CÓ THỂ THỰC HIỆN ĐƯỢC VÀ LẬP DỰ PHÒNG GIẢM GIÁ HÀNG TỒN KHO ➔ 18.)
+Trả lời câu hỏi: Khi đánh giá hàng tồn kho, doanh nghiệp vừa phải chọn một phương pháp tính giá trị phù hợp, vừa phải kiểm tra khả năng thu hồi giá trị hàng tồn kho. Nếu hàng tồn kho vẫn thu hồi đủ thì áp dụng phương pháp tính giá trị đã chọn; nếu giá trị không thu hồi đủ do hư hỏng, lỗi thời, giảm giá bán hoặc chi phí hoàn thiện/bán hàng tăng, thì phải ghi giảm giá gốc xuống giá trị thuần có thể thực hiện được.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>32</v>
+      </c>
+      <c r="B96" t="n">
+        <v>4</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Khi đánh giá hàng tồn kho, doanh nghiệp vừa phải chọn phương pháp tính giá trị vừa phải xem xét việc ghi giảm giá gốc trong trường hợp nào?</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hàng tồn kho được tính theo giá nào?"}, {"role": "assistant", "content": "Hàng tồn kho được tính theo giá gốc; nếu giá trị thuần có thể thực hiện được thấp hơn giá gốc thì phải tính theo giá trị thuần có thể thực hiện được."}]</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Khi đánh giá hàng tồn kho, doanh nghiệp áp dụng các phương pháp tính giá trị nào và khi nào phải ghi giảm giá gốc hàng tồn kho?</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 13.
+CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ TRỊ THUẦN CÓ THỂ THỰC HIỆN ĐƯỢC VÀ LẬP DỰ PHÒNG GIẢM GIÁ HÀNG TỒN KHO ➔ 18.</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Về phương pháp tính giá trị, hàng tồn kho được tính theo một trong các phương pháp: giá đích danh, bình quân gia quyền, nhập trước xuất trước, hoặc nhập sau xuất trước. Đây là nhóm quy định về cách xác định giá trị hàng tồn kho để ghi nhận và trình bày. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 13.)
+Ý từ nguồn 2: Riêng việc ghi giảm giá gốc phát sinh khi giá trị hàng tồn kho không thu hồi đủ, chẳng hạn hàng tồn kho bị hư hỏng, lỗi thời, giá bán bị giảm, hoặc chi phí hoàn thiện, chi phí để bán hàng tăng lên. Khi đó, ghi giảm giá gốc xuống bằng giá trị thuần có thể thực hiện được là phù hợp với nguyên tắc tài sản không được phản ánh lớn hơn giá trị thực hiện ước tính từ việc bán hay sử dụng. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ TRỊ THUẦN CÓ THỂ THỰC HIỆN ĐƯỢC VÀ LẬP DỰ PHÒNG GIẢM GIÁ HÀNG TỒN KHO ➔ 18.)
+Trả lời câu hỏi: Khi đánh giá hàng tồn kho, doanh nghiệp vừa phải chọn một phương pháp tính giá trị phù hợp, vừa phải kiểm tra khả năng thu hồi giá trị hàng tồn kho. Nếu hàng tồn kho vẫn thu hồi đủ thì áp dụng phương pháp tính giá trị đã chọn; nếu giá trị không thu hồi đủ do hư hỏng, lỗi thời, giảm giá bán hoặc chi phí hoàn thiện/bán hàng tăng, thì phải ghi giảm giá gốc xuống giá trị thuần có thể thực hiện được.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>32</v>
+      </c>
+      <c r="B97" t="n">
+        <v>4</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Khi đánh giá hàng tồn kho, doanh nghiệp vừa phải chọn phương pháp tính giá trị vừa phải xem xét việc ghi giảm giá gốc trong trường hợp nào?</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Hàng tồn kho được tính theo giá nào?"}, {"role": "assistant", "content": "Hàng tồn kho được tính theo giá gốc; nếu giá trị thuần có thể thực hiện được thấp hơn giá gốc thì phải tính theo giá trị thuần có thể thực hiện được."}]</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Khi đánh giá hàng tồn kho, doanh nghiệp áp dụng các phương pháp tính giá trị nào và khi nào phải ghi giảm giá gốc hàng tồn kho?</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 13.
+CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ TRỊ THUẦN CÓ THỂ THỰC HIỆN ĐƯỢC VÀ LẬP DỰ PHÒNG GIẢM GIÁ HÀNG TỒN KHO ➔ 18.</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Về phương pháp tính giá trị, hàng tồn kho được tính theo một trong các phương pháp: giá đích danh, bình quân gia quyền, nhập trước xuất trước, hoặc nhập sau xuất trước. Đây là nhóm quy định về cách xác định giá trị hàng tồn kho để ghi nhận và trình bày. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ PHƯƠNG PHÁP TÍNH GIÁ TRỊ HÀNG TỒN KHO ➔ 13.)
+Ý từ nguồn 2: Riêng việc ghi giảm giá gốc phát sinh khi giá trị hàng tồn kho không thu hồi đủ, chẳng hạn hàng tồn kho bị hư hỏng, lỗi thời, giá bán bị giảm, hoặc chi phí hoàn thiện, chi phí để bán hàng tăng lên. Khi đó, ghi giảm giá gốc xuống bằng giá trị thuần có thể thực hiện được là phù hợp với nguyên tắc tài sản không được phản ánh lớn hơn giá trị thực hiện ước tính từ việc bán hay sử dụng. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ TRỊ THUẦN CÓ THỂ THỰC HIỆN ĐƯỢC VÀ LẬP DỰ PHÒNG GIẢM GIÁ HÀNG TỒN KHO ➔ 18.)
+Trả lời câu hỏi: Khi đánh giá hàng tồn kho, doanh nghiệp vừa phải chọn một phương pháp tính giá trị phù hợp, vừa phải kiểm tra khả năng thu hồi giá trị hàng tồn kho. Nếu hàng tồn kho vẫn thu hồi đủ thì áp dụng phương pháp tính giá trị đã chọn; nếu giá trị không thu hồi đủ do hư hỏng, lỗi thời, giảm giá bán hoặc chi phí hoàn thiện/bán hàng tăng, thì phải ghi giảm giá gốc xuống giá trị thuần có thể thực hiện được.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>33</v>
+      </c>
+      <c r="B98" t="n">
+        <v>4</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp mua một phần mềm dùng lâu dài trong kinh doanh, nguyên giá xác định được và dự kiến tạo lợi ích kinh tế nhiều năm. Tuy nhiên chưa có bên nào cam kết mua lại phần mềm này khi hết thời gian sử dụng và cũng không có thị trường hoạt động cho phần mềm đó. Khi ghi nhận và tính giá trị còn lại cuối thời gian sử dụng, cần xử lý thế nào?</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định vô hình được hiểu là gì?"}, {"role": "assistant", "content": "Tài sản cố định vô hình là tài sản không có hình thái vật chất nhưng xác định được giá trị và do doanh nghiệp nắm giữ, sử dụng trong sản xuất kinh doanh, cung cấp dịch vụ hoặc cho thuê."}, {"role": "user", "content": "Với phần mềm thì có cần xét cả điều kiện ghi nhận và giá trị thanh lý không?"}, {"role": "assistant", "content": "Có. Cần xét trước việc có đủ điều kiện ghi nhận là tài sản cố định vô hình hay không, sau đó mới xem có cơ sở xác định giá trị thanh lý cuối thời gian sử dụng hay không."}]</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Phần mềm dùng lâu dài có đủ điều kiện ghi nhận là tài sản cố định vô hình không và nếu không có cam kết mua lại hoặc thị trường hoạt động thì giá trị thanh lý được xác định thế nào?</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ 16.
+CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ GIÁ TRỊ THANH LÝ ➔ 62.</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Một tài sản vô hình được ghi nhận là tài sản cố định vô hình khi thỏa mãn đồng thời định nghĩa về tài sản cố định vô hình và bốn tiêu chuẩn: chắc chắn thu được lợi ích kinh tế trong tương lai; nguyên giá xác định đáng tin cậy; thời gian sử dụng ước tính trên 1 năm; và đủ tiêu chuẩn giá trị theo quy định hiện hành. (Nguồn: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ 16.)
+Ý từ nguồn 2: Tài sản cố định vô hình có giá trị thanh lý khi có bên thứ ba thỏa thuận mua lại tài sản vào cuối thời gian sử dụng hữu ích, hoặc có thị trường hoạt động vào cuối thời gian sử dụng hữu ích và giá trị thanh lý xác định được thông qua giá thị trường. Nếu không có một trong hai điều kiện này thì giá trị thanh lý được xác định bằng không. (Nguồn: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ GIÁ TRỊ THANH LÝ ➔ 62.)
+Trả lời câu hỏi: Với phần mềm dùng lâu dài trong kinh doanh, nguyên giá xác định được và dự kiến tạo lợi ích kinh tế nhiều năm, doanh nghiệp có cơ sở xem xét ghi nhận là tài sản cố định vô hình nếu đồng thời đáp ứng đủ tiêu chuẩn giá trị theo quy định hiện hành. Tuy nhiên, vì không có bên thứ ba cam kết mua lại cuối thời gian sử dụng và cũng không có thị trường hoạt động cho phần mềm đó, giá trị thanh lý khi tính giá trị còn lại cuối thời gian sử dụng phải được xác định bằng 0.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>33</v>
+      </c>
+      <c r="B99" t="n">
+        <v>4</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp mua một phần mềm dùng lâu dài trong kinh doanh, nguyên giá xác định được và dự kiến tạo lợi ích kinh tế nhiều năm. Tuy nhiên chưa có bên nào cam kết mua lại phần mềm này khi hết thời gian sử dụng và cũng không có thị trường hoạt động cho phần mềm đó. Khi ghi nhận và tính giá trị còn lại cuối thời gian sử dụng, cần xử lý thế nào?</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định vô hình được hiểu là gì?"}, {"role": "assistant", "content": "Tài sản cố định vô hình là tài sản không có hình thái vật chất nhưng xác định được giá trị và do doanh nghiệp nắm giữ, sử dụng trong sản xuất kinh doanh, cung cấp dịch vụ hoặc cho thuê."}, {"role": "user", "content": "Với phần mềm thì có cần xét cả điều kiện ghi nhận và giá trị thanh lý không?"}, {"role": "assistant", "content": "Có. Cần xét trước việc có đủ điều kiện ghi nhận là tài sản cố định vô hình hay không, sau đó mới xem có cơ sở xác định giá trị thanh lý cuối thời gian sử dụng hay không."}]</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Phần mềm dùng lâu dài có đủ điều kiện ghi nhận là tài sản cố định vô hình không và nếu không có cam kết mua lại hoặc thị trường hoạt động thì giá trị thanh lý được xác định thế nào?</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ 16.
+CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ GIÁ TRỊ THANH LÝ ➔ 62.</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Một tài sản vô hình được ghi nhận là tài sản cố định vô hình khi thỏa mãn đồng thời định nghĩa về tài sản cố định vô hình và bốn tiêu chuẩn: chắc chắn thu được lợi ích kinh tế trong tương lai; nguyên giá xác định đáng tin cậy; thời gian sử dụng ước tính trên 1 năm; và đủ tiêu chuẩn giá trị theo quy định hiện hành. (Nguồn: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ 16.)
+Ý từ nguồn 2: Tài sản cố định vô hình có giá trị thanh lý khi có bên thứ ba thỏa thuận mua lại tài sản vào cuối thời gian sử dụng hữu ích, hoặc có thị trường hoạt động vào cuối thời gian sử dụng hữu ích và giá trị thanh lý xác định được thông qua giá thị trường. Nếu không có một trong hai điều kiện này thì giá trị thanh lý được xác định bằng không. (Nguồn: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ GIÁ TRỊ THANH LÝ ➔ 62.)
+Trả lời câu hỏi: Với phần mềm dùng lâu dài trong kinh doanh, nguyên giá xác định được và dự kiến tạo lợi ích kinh tế nhiều năm, doanh nghiệp có cơ sở xem xét ghi nhận là tài sản cố định vô hình nếu đồng thời đáp ứng đủ tiêu chuẩn giá trị theo quy định hiện hành. Tuy nhiên, vì không có bên thứ ba cam kết mua lại cuối thời gian sử dụng và cũng không có thị trường hoạt động cho phần mềm đó, giá trị thanh lý khi tính giá trị còn lại cuối thời gian sử dụng phải được xác định bằng 0.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>33</v>
+      </c>
+      <c r="B100" t="n">
+        <v>4</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp mua một phần mềm dùng lâu dài trong kinh doanh, nguyên giá xác định được và dự kiến tạo lợi ích kinh tế nhiều năm. Tuy nhiên chưa có bên nào cam kết mua lại phần mềm này khi hết thời gian sử dụng và cũng không có thị trường hoạt động cho phần mềm đó. Khi ghi nhận và tính giá trị còn lại cuối thời gian sử dụng, cần xử lý thế nào?</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Tài sản cố định vô hình được hiểu là gì?"}, {"role": "assistant", "content": "Tài sản cố định vô hình là tài sản không có hình thái vật chất nhưng xác định được giá trị và do doanh nghiệp nắm giữ, sử dụng trong sản xuất kinh doanh, cung cấp dịch vụ hoặc cho thuê."}, {"role": "user", "content": "Với phần mềm thì có cần xét cả điều kiện ghi nhận và giá trị thanh lý không?"}, {"role": "assistant", "content": "Có. Cần xét trước việc có đủ điều kiện ghi nhận là tài sản cố định vô hình hay không, sau đó mới xem có cơ sở xác định giá trị thanh lý cuối thời gian sử dụng hay không."}]</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Phần mềm dùng lâu dài có đủ điều kiện ghi nhận là tài sản cố định vô hình không và nếu không có cam kết mua lại hoặc thị trường hoạt động thì giá trị thanh lý được xác định thế nào?</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ 16.
+CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ GIÁ TRỊ THANH LÝ ➔ 62.</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Một tài sản vô hình được ghi nhận là tài sản cố định vô hình khi thỏa mãn đồng thời định nghĩa về tài sản cố định vô hình và bốn tiêu chuẩn: chắc chắn thu được lợi ích kinh tế trong tương lai; nguyên giá xác định đáng tin cậy; thời gian sử dụng ước tính trên 1 năm; và đủ tiêu chuẩn giá trị theo quy định hiện hành. (Nguồn: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ 16.)
+Ý từ nguồn 2: Tài sản cố định vô hình có giá trị thanh lý khi có bên thứ ba thỏa thuận mua lại tài sản vào cuối thời gian sử dụng hữu ích, hoặc có thị trường hoạt động vào cuối thời gian sử dụng hữu ích và giá trị thanh lý xác định được thông qua giá thị trường. Nếu không có một trong hai điều kiện này thì giá trị thanh lý được xác định bằng không. (Nguồn: CHUẨN MỰC SỐ 04 - TÀI SẢN CỐ ĐỊNH VÔ HÌNH ➔ NỘI DUNG CỦA CHUẨN MỰC GHI NHẬN VÀ XÁC ĐỊNH GIÁ TRỊ BAN ĐẦU ➔ GIÁ TRỊ THANH LÝ ➔ 62.)
+Trả lời câu hỏi: Với phần mềm dùng lâu dài trong kinh doanh, nguyên giá xác định được và dự kiến tạo lợi ích kinh tế nhiều năm, doanh nghiệp có cơ sở xem xét ghi nhận là tài sản cố định vô hình nếu đồng thời đáp ứng đủ tiêu chuẩn giá trị theo quy định hiện hành. Tuy nhiên, vì không có bên thứ ba cam kết mua lại cuối thời gian sử dụng và cũng không có thị trường hoạt động cho phần mềm đó, giá trị thanh lý khi tính giá trị còn lại cuối thời gian sử dụng phải được xác định bằng 0.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>34</v>
+      </c>
+      <c r="B101" t="n">
+        <v>4</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp mua hàng tồn kho và phát sinh giá mua, thuế không được hoàn lại, vận chuyển, bốc xếp, đồng thời có chi phí bán hàng và chi phí quản lý doanh nghiệp. Khi xác định giá gốc hàng tồn kho, nên đưa khoản nào vào và loại khoản nào ra?</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Giá gốc hàng tồn kho gồm những chi phí nào?"}, {"role": "assistant", "content": "Giá gốc hàng tồn kho gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác phát sinh để có được hàng tồn kho ở địa điểm và trạng thái hiện tại."}, {"role": "user", "content": "Nếu có nhiều loại chi phí phát sinh cùng lúc thì cần phân loại đúng đúng không?"}, {"role": "assistant", "content": "Đúng. Cần xác định khoản nào thuộc chi phí mua hoặc chi phí liên quan trực tiếp, và khoản nào không được tính vào giá gốc hàng tồn kho."}]</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Khi mua hàng tồn kho, các khoản chi phí nào được tính vào giá gốc và các khoản nào phải loại khỏi giá gốc trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí mua ➔ 06.
+CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Chi phí mua của hàng tồn kho bao gồm giá mua, các loại thuế không được hoàn lại, chi phí vận chuyển, bốc xếp, bảo quản trong quá trình mua hàng và các chi phí khác liên quan trực tiếp đến việc mua hàng tồn kho. Các khoản chiết khấu thương mại và giảm giá hàng mua do hàng mua không đúng quy cách, phẩm chất được trừ khỏi chi phí mua. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí mua ➔ 06.)
+Ý từ nguồn 2: Các khoản không được tính vào giá gốc hàng tồn kho gồm chi phí nguyên liệu, vật liệu, nhân công và chi phí sản xuất, kinh doanh khác phát sinh trên mức bình thường; chi phí bảo quản hàng tồn kho, trừ trường hợp cần thiết cho quá trình sản xuất tiếp theo hoặc thuộc chi phí mua; chi phí bán hàng; và chi phí quản lý doanh nghiệp. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.)
+Trả lời câu hỏi: Trong tình huống doanh nghiệp mua hàng tồn kho, giá mua, thuế không được hoàn lại, vận chuyển, bốc xếp và các chi phí trực tiếp trong quá trình mua hàng được đưa vào giá gốc hàng tồn kho. Ngược lại, chi phí bán hàng và chi phí quản lý doanh nghiệp phải loại khỏi giá gốc. Nếu có chi phí bất thường vượt mức bình thường hoặc chi phí bảo quản không cần thiết cho quá trình sản xuất tiếp theo thì cũng không đưa vào giá gốc.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>34</v>
+      </c>
+      <c r="B102" t="n">
+        <v>4</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp mua hàng tồn kho và phát sinh giá mua, thuế không được hoàn lại, vận chuyển, bốc xếp, đồng thời có chi phí bán hàng và chi phí quản lý doanh nghiệp. Khi xác định giá gốc hàng tồn kho, nên đưa khoản nào vào và loại khoản nào ra?</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Giá gốc hàng tồn kho gồm những chi phí nào?"}, {"role": "assistant", "content": "Giá gốc hàng tồn kho gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác phát sinh để có được hàng tồn kho ở địa điểm và trạng thái hiện tại."}, {"role": "user", "content": "Nếu có nhiều loại chi phí phát sinh cùng lúc thì cần phân loại đúng đúng không?"}, {"role": "assistant", "content": "Đúng. Cần xác định khoản nào thuộc chi phí mua hoặc chi phí liên quan trực tiếp, và khoản nào không được tính vào giá gốc hàng tồn kho."}]</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Khi mua hàng tồn kho, các khoản chi phí nào được tính vào giá gốc và các khoản nào phải loại khỏi giá gốc trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí mua ➔ 06.
+CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Chi phí mua của hàng tồn kho bao gồm giá mua, các loại thuế không được hoàn lại, chi phí vận chuyển, bốc xếp, bảo quản trong quá trình mua hàng và các chi phí khác liên quan trực tiếp đến việc mua hàng tồn kho. Các khoản chiết khấu thương mại và giảm giá hàng mua do hàng mua không đúng quy cách, phẩm chất được trừ khỏi chi phí mua. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí mua ➔ 06.)
+Ý từ nguồn 2: Các khoản không được tính vào giá gốc hàng tồn kho gồm chi phí nguyên liệu, vật liệu, nhân công và chi phí sản xuất, kinh doanh khác phát sinh trên mức bình thường; chi phí bảo quản hàng tồn kho, trừ trường hợp cần thiết cho quá trình sản xuất tiếp theo hoặc thuộc chi phí mua; chi phí bán hàng; và chi phí quản lý doanh nghiệp. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.)
+Trả lời câu hỏi: Trong tình huống doanh nghiệp mua hàng tồn kho, giá mua, thuế không được hoàn lại, vận chuyển, bốc xếp và các chi phí trực tiếp trong quá trình mua hàng được đưa vào giá gốc hàng tồn kho. Ngược lại, chi phí bán hàng và chi phí quản lý doanh nghiệp phải loại khỏi giá gốc. Nếu có chi phí bất thường vượt mức bình thường hoặc chi phí bảo quản không cần thiết cho quá trình sản xuất tiếp theo thì cũng không đưa vào giá gốc.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>34</v>
+      </c>
+      <c r="B103" t="n">
+        <v>4</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp mua hàng tồn kho và phát sinh giá mua, thuế không được hoàn lại, vận chuyển, bốc xếp, đồng thời có chi phí bán hàng và chi phí quản lý doanh nghiệp. Khi xác định giá gốc hàng tồn kho, nên đưa khoản nào vào và loại khoản nào ra?</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Giá gốc hàng tồn kho gồm những chi phí nào?"}, {"role": "assistant", "content": "Giá gốc hàng tồn kho gồm chi phí mua, chi phí chế biến và các chi phí liên quan trực tiếp khác phát sinh để có được hàng tồn kho ở địa điểm và trạng thái hiện tại."}, {"role": "user", "content": "Nếu có nhiều loại chi phí phát sinh cùng lúc thì cần phân loại đúng đúng không?"}, {"role": "assistant", "content": "Đúng. Cần xác định khoản nào thuộc chi phí mua hoặc chi phí liên quan trực tiếp, và khoản nào không được tính vào giá gốc hàng tồn kho."}]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Khi mua hàng tồn kho, các khoản chi phí nào được tính vào giá gốc và các khoản nào phải loại khỏi giá gốc trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí mua ➔ 06.
+CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Chi phí mua của hàng tồn kho bao gồm giá mua, các loại thuế không được hoàn lại, chi phí vận chuyển, bốc xếp, bảo quản trong quá trình mua hàng và các chi phí khác liên quan trực tiếp đến việc mua hàng tồn kho. Các khoản chiết khấu thương mại và giảm giá hàng mua do hàng mua không đúng quy cách, phẩm chất được trừ khỏi chi phí mua. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí mua ➔ 06.)
+Ý từ nguồn 2: Các khoản không được tính vào giá gốc hàng tồn kho gồm chi phí nguyên liệu, vật liệu, nhân công và chi phí sản xuất, kinh doanh khác phát sinh trên mức bình thường; chi phí bảo quản hàng tồn kho, trừ trường hợp cần thiết cho quá trình sản xuất tiếp theo hoặc thuộc chi phí mua; chi phí bán hàng; và chi phí quản lý doanh nghiệp. (Nguồn: CHUẨN MỰC SỐ 02 - HÀNG TỒN KHO ➔ NỘI DUNG CHUẨN MỰC ➔ GIÁ GỐC HÀNG TỒN KHO ➔ Chi phí không tính vào giá gốc hàng tồn kho ➔ 11.)
+Trả lời câu hỏi: Trong tình huống doanh nghiệp mua hàng tồn kho, giá mua, thuế không được hoàn lại, vận chuyển, bốc xếp và các chi phí trực tiếp trong quá trình mua hàng được đưa vào giá gốc hàng tồn kho. Ngược lại, chi phí bán hàng và chi phí quản lý doanh nghiệp phải loại khỏi giá gốc. Nếu có chi phí bất thường vượt mức bình thường hoặc chi phí bảo quản không cần thiết cho quá trình sản xuất tiếp theo thì cũng không đưa vào giá gốc.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>35</v>
+      </c>
+      <c r="B104" t="n">
+        <v>4</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp bán hàng có chiết khấu thương mại và hàng đã giao cho người mua. Nếu muốn ghi nhận doanh thu, doanh nghiệp cần xác định số doanh thu như thế nào và phải kiểm tra thêm những điều kiện gì?</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Doanh thu là gì?"}, {"role": "assistant", "content": "Doanh thu là tổng giá trị lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán từ hoạt động sản xuất kinh doanh thông thường và góp phần làm tăng vốn chủ sở hữu."}]</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Khi bán hàng có chiết khấu thương mại, doanh thu được xác định như thế nào và cần thỏa mãn điều kiện gì để được ghi nhận trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ XÁC ĐỊNH DOANH THU ➔ 06.
+CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Doanh thu phát sinh từ giao dịch được xác định theo thỏa thuận giữa doanh nghiệp với bên mua hoặc bên sử dụng tài sản. Doanh thu được xác định bằng giá trị hợp lý của khoản đã thu hoặc sẽ thu được, sau khi trừ chiết khấu thương mại, chiết khấu thanh toán, giảm giá hàng bán và giá trị hàng bán bị trả lại. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ XÁC ĐỊNH DOANH THU ➔ 06.)
+Ý từ nguồn 2: Doanh thu bán hàng chỉ được ghi nhận khi đồng thời thỏa mãn năm điều kiện: đã chuyển giao phần lớn rủi ro và lợi ích gắn với quyền sở hữu sản phẩm hoặc hàng hóa cho người mua; không còn nắm giữ quyền quản lý hoặc kiểm soát hàng hóa; doanh thu được xác định tương đối chắc chắn; đã thu được hoặc sẽ thu được lợi ích kinh tế; và xác định được chi phí liên quan đến giao dịch bán hàng. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.)
+Trả lời câu hỏi: Với giao dịch bán hàng có chiết khấu thương mại, doanh nghiệp phải xác định số doanh thu theo giá trị hợp lý của khoản đã thu hoặc sẽ thu được sau khi trừ khoản chiết khấu đó. Tuy nhiên, việc xác định được số doanh thu chưa đủ để ghi nhận doanh thu. Doanh nghiệp chỉ được ghi nhận doanh thu bán hàng nếu đồng thời thỏa mãn đầy đủ năm điều kiện ghi nhận, bao gồm chuyển giao phần lớn rủi ro và lợi ích, không còn kiểm soát hàng hóa, doanh thu xác định tương đối chắc chắn, thu được hoặc sẽ thu được lợi ích kinh tế và xác định được chi phí liên quan.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>35</v>
+      </c>
+      <c r="B105" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp bán hàng có chiết khấu thương mại và hàng đã giao cho người mua. Nếu muốn ghi nhận doanh thu, doanh nghiệp cần xác định số doanh thu như thế nào và phải kiểm tra thêm những điều kiện gì?</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Doanh thu là gì?"}, {"role": "assistant", "content": "Doanh thu là tổng giá trị lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán từ hoạt động sản xuất kinh doanh thông thường và góp phần làm tăng vốn chủ sở hữu."}]</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Khi bán hàng có chiết khấu thương mại, doanh thu được xác định như thế nào và cần thỏa mãn điều kiện gì để được ghi nhận trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ XÁC ĐỊNH DOANH THU ➔ 06.
+CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Doanh thu phát sinh từ giao dịch được xác định theo thỏa thuận giữa doanh nghiệp với bên mua hoặc bên sử dụng tài sản. Doanh thu được xác định bằng giá trị hợp lý của khoản đã thu hoặc sẽ thu được, sau khi trừ chiết khấu thương mại, chiết khấu thanh toán, giảm giá hàng bán và giá trị hàng bán bị trả lại. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ XÁC ĐỊNH DOANH THU ➔ 06.)
+Ý từ nguồn 2: Doanh thu bán hàng chỉ được ghi nhận khi đồng thời thỏa mãn năm điều kiện: đã chuyển giao phần lớn rủi ro và lợi ích gắn với quyền sở hữu sản phẩm hoặc hàng hóa cho người mua; không còn nắm giữ quyền quản lý hoặc kiểm soát hàng hóa; doanh thu được xác định tương đối chắc chắn; đã thu được hoặc sẽ thu được lợi ích kinh tế; và xác định được chi phí liên quan đến giao dịch bán hàng. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.)
+Trả lời câu hỏi: Với giao dịch bán hàng có chiết khấu thương mại, doanh nghiệp phải xác định số doanh thu theo giá trị hợp lý của khoản đã thu hoặc sẽ thu được sau khi trừ khoản chiết khấu đó. Tuy nhiên, việc xác định được số doanh thu chưa đủ để ghi nhận doanh thu. Doanh nghiệp chỉ được ghi nhận doanh thu bán hàng nếu đồng thời thỏa mãn đầy đủ năm điều kiện ghi nhận, bao gồm chuyển giao phần lớn rủi ro và lợi ích, không còn kiểm soát hàng hóa, doanh thu xác định tương đối chắc chắn, thu được hoặc sẽ thu được lợi ích kinh tế và xác định được chi phí liên quan.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>35</v>
+      </c>
+      <c r="B106" t="n">
+        <v>4</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp bán hàng có chiết khấu thương mại và hàng đã giao cho người mua. Nếu muốn ghi nhận doanh thu, doanh nghiệp cần xác định số doanh thu như thế nào và phải kiểm tra thêm những điều kiện gì?</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>[{"role": "user", "content": "Doanh thu là gì?"}, {"role": "assistant", "content": "Doanh thu là tổng giá trị lợi ích kinh tế doanh nghiệp thu được trong kỳ kế toán từ hoạt động sản xuất kinh doanh thông thường và góp phần làm tăng vốn chủ sở hữu."}]</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Khi bán hàng có chiết khấu thương mại, doanh thu được xác định như thế nào và cần thỏa mãn điều kiện gì để được ghi nhận trong kế toán VAS?</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ XÁC ĐỊNH DOANH THU ➔ 06.
+CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Ý từ nguồn 1: Doanh thu phát sinh từ giao dịch được xác định theo thỏa thuận giữa doanh nghiệp với bên mua hoặc bên sử dụng tài sản. Doanh thu được xác định bằng giá trị hợp lý của khoản đã thu hoặc sẽ thu được, sau khi trừ chiết khấu thương mại, chiết khấu thanh toán, giảm giá hàng bán và giá trị hàng bán bị trả lại. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ XÁC ĐỊNH DOANH THU ➔ 06.)
+Ý từ nguồn 2: Doanh thu bán hàng chỉ được ghi nhận khi đồng thời thỏa mãn năm điều kiện: đã chuyển giao phần lớn rủi ro và lợi ích gắn với quyền sở hữu sản phẩm hoặc hàng hóa cho người mua; không còn nắm giữ quyền quản lý hoặc kiểm soát hàng hóa; doanh thu được xác định tương đối chắc chắn; đã thu được hoặc sẽ thu được lợi ích kinh tế; và xác định được chi phí liên quan đến giao dịch bán hàng. (Nguồn: CHUẨN MỰC SỐ 14 - DOANH THU VÀ THU NHẬP KHÁC ➔ NỘI DUNG CHUẨN MỰC ➔ DOANH THU BÁN HÀNG ➔ 10.)
+Trả lời câu hỏi: Với giao dịch bán hàng có chiết khấu thương mại, doanh nghiệp phải xác định số doanh thu theo giá trị hợp lý của khoản đã thu hoặc sẽ thu được sau khi trừ khoản chiết khấu đó. Tuy nhiên, việc xác định được số doanh thu chưa đủ để ghi nhận doanh thu. Doanh nghiệp chỉ được ghi nhận doanh thu bán hàng nếu đồng thời thỏa mãn đầy đủ năm điều kiện ghi nhận, bao gồm chuyển giao phần lớn rủi ro và lợi ích, không còn kiểm soát hàng hóa, doanh thu xác định tương đối chắc chắn, thu được hoặc sẽ thu được lợi ích kinh tế và xác định được chi phí liên quan.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>LỖI: '\n    "standalone_query"'</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>'\n    "standalone_query"'</t>
+        </is>
       </c>
     </row>
   </sheetData>
